--- a/sprint-9/Task2/tco-model.xlsx
+++ b/sprint-9/Task2/tco-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ya.practicum\solution-architect\ya.solution-architecture-tasks\sprint-9\Task2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF834B38-60DE-43D8-9B32-400B996D5AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031ABB52-0289-4D61-9832-BA4BAD31B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="3360" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" r:id="rId1"/>
@@ -935,6 +935,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -942,10 +951,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -958,16 +963,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1272,10 +1272,10 @@
       <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="51" t="s">
+      <c r="D14" s="33" t="s">
         <v>191</v>
       </c>
     </row>
@@ -1283,10 +1283,10 @@
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="51" t="s">
+      <c r="D15" s="33" t="s">
         <v>191</v>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="34" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1377,10 +1377,10 @@
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="33"/>
+      <c r="C28" s="36"/>
     </row>
     <row r="29" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2828,24 +2828,24 @@
     </row>
     <row r="31" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
     </row>
     <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
     </row>
     <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3906,31 +3906,31 @@
         <v>64</v>
       </c>
       <c r="D7" s="17">
-        <v>5400</v>
+        <v>18525.259999999998</v>
       </c>
       <c r="E7" s="22">
         <f t="array" ref="E7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),1))</f>
-        <v>5400</v>
+        <v>18525.259999999998</v>
       </c>
       <c r="F7" s="22">
         <f t="array" ref="F7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),2))</f>
-        <v>21600</v>
+        <v>74101.039999999994</v>
       </c>
       <c r="G7" s="22">
         <f t="array" ref="G7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),3))</f>
-        <v>54000</v>
+        <v>185252.59999999998</v>
       </c>
       <c r="H7" s="22">
         <f t="array" ref="H7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),4))</f>
-        <v>90000</v>
+        <v>308754.33333333331</v>
       </c>
       <c r="I7" s="22">
         <f t="array" ref="I7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),5))</f>
-        <v>126000</v>
+        <v>432256.06666666659</v>
       </c>
       <c r="J7" s="22">
         <f t="shared" ref="J7:J14" si="0">SUM(E7:I7)</f>
-        <v>297000</v>
+        <v>1018889.2999999998</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="24" t="s">
@@ -3945,31 +3945,31 @@
         <v>64</v>
       </c>
       <c r="D8" s="17">
-        <v>5400</v>
+        <v>27787.9</v>
       </c>
       <c r="E8" s="22">
         <f t="array" ref="E8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),1))</f>
-        <v>5400</v>
+        <v>27787.9</v>
       </c>
       <c r="F8" s="22">
         <f t="array" ref="F8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),2))</f>
-        <v>21600</v>
+        <v>111151.6</v>
       </c>
       <c r="G8" s="22">
         <f t="array" ref="G8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),3))</f>
-        <v>54000</v>
+        <v>277879</v>
       </c>
       <c r="H8" s="22">
         <f t="array" ref="H8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),4))</f>
-        <v>90000</v>
+        <v>463131.66666666674</v>
       </c>
       <c r="I8" s="22">
         <f t="array" ref="I8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),5))</f>
-        <v>126000</v>
+        <v>648384.33333333337</v>
       </c>
       <c r="J8" s="22">
         <f t="shared" si="0"/>
-        <v>297000</v>
+        <v>1528334.5</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="24" t="s">
@@ -3984,31 +3984,31 @@
         <v>64</v>
       </c>
       <c r="D9" s="17">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="E9" s="22">
         <f t="array" ref="E9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),1))</f>
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="F9" s="22">
         <f t="array" ref="F9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),2))</f>
-        <v>5760</v>
+        <v>7200</v>
       </c>
       <c r="G9" s="22">
         <f t="array" ref="G9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),3))</f>
-        <v>14400</v>
+        <v>18000</v>
       </c>
       <c r="H9" s="22">
         <f t="array" ref="H9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),4))</f>
-        <v>24000</v>
+        <v>30000.000000000004</v>
       </c>
       <c r="I9" s="22">
         <f t="array" ref="I9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),5))</f>
-        <v>33600</v>
+        <v>42000</v>
       </c>
       <c r="J9" s="22">
         <f t="shared" si="0"/>
-        <v>79200</v>
+        <v>99000</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="24" t="s">
@@ -4023,31 +4023,31 @@
         <v>64</v>
       </c>
       <c r="D10" s="17">
-        <v>1260.0000000000002</v>
+        <v>5430</v>
       </c>
       <c r="E10" s="22">
         <f t="array" ref="E10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),1))</f>
-        <v>1260.0000000000002</v>
+        <v>5430</v>
       </c>
       <c r="F10" s="22">
         <f t="array" ref="F10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),2))</f>
-        <v>5040.0000000000009</v>
+        <v>21720</v>
       </c>
       <c r="G10" s="22">
         <f t="array" ref="G10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),3))</f>
-        <v>12600.000000000002</v>
+        <v>54300</v>
       </c>
       <c r="H10" s="22">
         <f t="array" ref="H10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),4))</f>
-        <v>21000.000000000004</v>
+        <v>90500</v>
       </c>
       <c r="I10" s="22">
         <f t="array" ref="I10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),5))</f>
-        <v>29400.000000000004</v>
+        <v>126700</v>
       </c>
       <c r="J10" s="22">
         <f t="shared" si="0"/>
-        <v>69300.000000000015</v>
+        <v>298650</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="24" t="s">
@@ -4062,31 +4062,31 @@
         <v>64</v>
       </c>
       <c r="D11" s="17">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="E11" s="22">
         <f t="array" ref="E11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),1))</f>
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="F11" s="22">
         <f t="array" ref="F11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),2))</f>
-        <v>2160</v>
+        <v>0</v>
       </c>
       <c r="G11" s="22">
         <f t="array" ref="G11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),3))</f>
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H11" s="22">
         <f t="array" ref="H11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),4))</f>
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="22">
         <f t="array" ref="I11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),5))</f>
-        <v>12600</v>
+        <v>0</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="0"/>
-        <v>29700</v>
+        <v>0</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="24" t="s">
@@ -4101,31 +4101,31 @@
         <v>64</v>
       </c>
       <c r="D12" s="17">
-        <v>1260.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="E12" s="22">
         <f t="array" ref="E12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),1))</f>
-        <v>1260.0000000000002</v>
+        <v>0</v>
       </c>
       <c r="F12" s="22">
         <f t="array" ref="F12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),2))</f>
-        <v>5040.0000000000009</v>
+        <v>0</v>
       </c>
       <c r="G12" s="22">
         <f t="array" ref="G12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),3))</f>
-        <v>12600.000000000002</v>
+        <v>0</v>
       </c>
       <c r="H12" s="22">
         <f t="array" ref="H12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),4))</f>
-        <v>21000.000000000004</v>
+        <v>0</v>
       </c>
       <c r="I12" s="22">
         <f t="array" ref="I12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),5))</f>
-        <v>29400.000000000004</v>
+        <v>0</v>
       </c>
       <c r="J12" s="22">
         <f t="shared" si="0"/>
-        <v>69300.000000000015</v>
+        <v>0</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="24" t="s">
@@ -4140,31 +4140,31 @@
         <v>90</v>
       </c>
       <c r="D13" s="17">
-        <v>0</v>
+        <v>11152.83</v>
       </c>
       <c r="E13" s="22">
         <f t="array" ref="E13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>11152.83</v>
       </c>
       <c r="F13" s="22">
         <f t="array" ref="F13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>12045.056400000001</v>
       </c>
       <c r="G13" s="22">
         <f t="array" ref="G13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>13008.660912000001</v>
       </c>
       <c r="H13" s="22">
         <f t="array" ref="H13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>14049.353784960002</v>
       </c>
       <c r="I13" s="22">
         <f t="array" ref="I13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>15173.302087756803</v>
       </c>
       <c r="J13" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>65429.203184716811</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="24" t="s">
@@ -4216,31 +4216,31 @@
       <c r="D15" s="26"/>
       <c r="E15" s="27">
         <f t="shared" ref="E15:J15" si="1">SUM(E7:E14)</f>
-        <v>15300</v>
+        <v>64695.990000000005</v>
       </c>
       <c r="F15" s="27">
         <f t="shared" si="1"/>
-        <v>61200</v>
+        <v>226217.69640000002</v>
       </c>
       <c r="G15" s="27">
         <f t="shared" si="1"/>
-        <v>153000</v>
+        <v>548440.26091199997</v>
       </c>
       <c r="H15" s="27">
         <f t="shared" si="1"/>
-        <v>255000</v>
+        <v>906435.35378496</v>
       </c>
       <c r="I15" s="27">
         <f t="shared" si="1"/>
-        <v>357000</v>
+        <v>1264513.7020877567</v>
       </c>
       <c r="J15" s="27">
         <f t="shared" si="1"/>
-        <v>841500</v>
+        <v>3010303.0031847167</v>
       </c>
       <c r="K15" s="28">
         <f>IFERROR(J15/$J$51,0)</f>
-        <v>2.2919949388913913E-2</v>
+        <v>7.9834206777594133E-2</v>
       </c>
       <c r="L15" s="26"/>
     </row>
@@ -4270,31 +4270,31 @@
         <v>64</v>
       </c>
       <c r="D18" s="17">
-        <v>1440</v>
+        <v>1200</v>
       </c>
       <c r="E18" s="22">
         <f t="array" ref="E18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),1))</f>
-        <v>1440</v>
+        <v>1200</v>
       </c>
       <c r="F18" s="22">
         <f t="array" ref="F18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),2))</f>
-        <v>5760</v>
+        <v>4800</v>
       </c>
       <c r="G18" s="22">
         <f t="array" ref="G18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),3))</f>
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="H18" s="22">
         <f t="array" ref="H18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),4))</f>
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="I18" s="22">
         <f t="array" ref="I18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),5))</f>
-        <v>33600</v>
+        <v>28000</v>
       </c>
       <c r="J18" s="22">
         <f t="shared" ref="J18:J23" si="2">SUM(E18:I18)</f>
-        <v>79200</v>
+        <v>66000</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="24" t="s">
@@ -4309,31 +4309,31 @@
         <v>90</v>
       </c>
       <c r="D19" s="17">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="E19" s="22">
         <f t="array" ref="E19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),1))</f>
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="F19" s="22">
         <f t="array" ref="F19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),2))</f>
-        <v>583.20000000000005</v>
+        <v>648</v>
       </c>
       <c r="G19" s="22">
         <f t="array" ref="G19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),3))</f>
-        <v>629.85600000000011</v>
+        <v>699.84</v>
       </c>
       <c r="H19" s="22">
         <f t="array" ref="H19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),4))</f>
-        <v>680.24448000000007</v>
+        <v>755.82720000000006</v>
       </c>
       <c r="I19" s="22">
         <f t="array" ref="I19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),5))</f>
-        <v>734.66403840000021</v>
+        <v>816.29337600000019</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="2"/>
-        <v>3167.9645184000001</v>
+        <v>3519.9605760000004</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="24" t="s">
@@ -4348,31 +4348,31 @@
         <v>64</v>
       </c>
       <c r="D20" s="17">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="E20" s="22">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),1))</f>
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="F20" s="22">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),2))</f>
-        <v>2880</v>
+        <v>0</v>
       </c>
       <c r="G20" s="22">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),3))</f>
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="22">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),4))</f>
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="I20" s="22">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),5))</f>
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="2"/>
-        <v>39600</v>
+        <v>0</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="24" t="s">
@@ -4387,31 +4387,31 @@
         <v>90</v>
       </c>
       <c r="D21" s="17">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E21" s="22">
         <f t="array" ref="E21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F21" s="22">
         <f t="array" ref="F21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="G21" s="22">
         <f t="array" ref="G21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>699.84</v>
       </c>
       <c r="H21" s="22">
         <f t="array" ref="H21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>755.82720000000006</v>
       </c>
       <c r="I21" s="22">
         <f t="array" ref="I21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>816.29337600000019</v>
       </c>
       <c r="J21" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3519.9605760000004</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="24" t="s">
@@ -4502,31 +4502,31 @@
       <c r="D24" s="26"/>
       <c r="E24" s="27">
         <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" si="3"/>
-        <v>9223.2000000000007</v>
+        <v>6096</v>
       </c>
       <c r="G24" s="27">
         <f t="shared" si="3"/>
-        <v>22229.856</v>
+        <v>13399.68</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="3"/>
-        <v>36680.244480000001</v>
+        <v>21511.654399999999</v>
       </c>
       <c r="I24" s="27">
         <f t="shared" si="3"/>
-        <v>51134.664038399998</v>
+        <v>29632.586752000003</v>
       </c>
       <c r="J24" s="27">
         <f t="shared" si="3"/>
-        <v>121967.9645184</v>
+        <v>73039.921151999995</v>
       </c>
       <c r="K24" s="28">
         <f>IFERROR(J24/$J$51,0)</f>
-        <v>3.3220434626625977E-3</v>
+        <v>1.9370422718573538E-3</v>
       </c>
       <c r="L24" s="26"/>
     </row>
@@ -4556,32 +4556,31 @@
         <v>97</v>
       </c>
       <c r="D27" s="17">
-        <f>Допущения!C10*0.02</f>
-        <v>150000</v>
+        <v>137500</v>
       </c>
       <c r="E27" s="22">
         <f t="array" ref="E27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),1))</f>
-        <v>150000</v>
+        <v>137500</v>
       </c>
       <c r="F27" s="22">
         <f t="array" ref="F27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),2))</f>
-        <v>936000</v>
+        <v>858000</v>
       </c>
       <c r="G27" s="22">
         <f t="array" ref="G27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),3))</f>
-        <v>3240000</v>
+        <v>2970000</v>
       </c>
       <c r="H27" s="22">
         <f t="array" ref="H27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),4))</f>
-        <v>6720000</v>
+        <v>6160000</v>
       </c>
       <c r="I27" s="22">
         <f t="array" ref="I27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),5))</f>
-        <v>10440000</v>
+        <v>9570000</v>
       </c>
       <c r="J27" s="22">
         <f t="shared" ref="J27:J31" si="4">SUM(E27:I27)</f>
-        <v>21486000</v>
+        <v>19695500</v>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="24" t="s">
@@ -4596,32 +4595,31 @@
         <v>95</v>
       </c>
       <c r="D28" s="17">
-        <f>Допущения!C8*0.05</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E28" s="22">
         <f t="array" ref="E28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),1))</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="F28" s="22">
         <f t="array" ref="F28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),2))</f>
-        <v>90000</v>
+        <v>108000</v>
       </c>
       <c r="G28" s="22">
         <f t="array" ref="G28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),3))</f>
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="H28" s="22">
         <f t="array" ref="H28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),4))</f>
-        <v>600000</v>
+        <v>720000</v>
       </c>
       <c r="I28" s="22">
         <f t="array" ref="I28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),5))</f>
-        <v>900000</v>
+        <v>1080000</v>
       </c>
       <c r="J28" s="22">
         <f t="shared" si="4"/>
-        <v>1905000</v>
+        <v>2286000</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="24" t="s">
@@ -4636,32 +4634,31 @@
         <v>95</v>
       </c>
       <c r="D29" s="17">
-        <f>Допущения!C8*0.02</f>
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="E29" s="22">
         <f t="array" ref="E29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),1))</f>
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="F29" s="22">
         <f t="array" ref="F29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),2))</f>
-        <v>36000</v>
+        <v>43200</v>
       </c>
       <c r="G29" s="22">
         <f t="array" ref="G29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),3))</f>
-        <v>120000</v>
+        <v>144000</v>
       </c>
       <c r="H29" s="22">
         <f t="array" ref="H29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),4))</f>
-        <v>240000</v>
+        <v>288000</v>
       </c>
       <c r="I29" s="22">
         <f t="array" ref="I29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),5))</f>
-        <v>360000</v>
+        <v>432000</v>
       </c>
       <c r="J29" s="22">
         <f t="shared" si="4"/>
-        <v>762000</v>
+        <v>914400</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="24" t="s">
@@ -4753,31 +4750,31 @@
       <c r="D32" s="26"/>
       <c r="E32" s="27">
         <f t="shared" ref="E32:J32" si="5">SUM(E27:E31)</f>
-        <v>201000</v>
+        <v>192700</v>
       </c>
       <c r="F32" s="27">
         <f t="shared" si="5"/>
-        <v>1242000</v>
+        <v>1189200</v>
       </c>
       <c r="G32" s="27">
         <f t="shared" si="5"/>
-        <v>4260000</v>
+        <v>4074000</v>
       </c>
       <c r="H32" s="27">
         <f t="shared" si="5"/>
-        <v>8760000</v>
+        <v>8368000</v>
       </c>
       <c r="I32" s="27">
         <f t="shared" si="5"/>
-        <v>13500000</v>
+        <v>12882000</v>
       </c>
       <c r="J32" s="27">
         <f t="shared" si="5"/>
-        <v>27963000</v>
+        <v>26705900</v>
       </c>
       <c r="K32" s="28">
         <f>IFERROR(J32/$J$51,0)</f>
-        <v>0.76162869252786669</v>
+        <v>0.70824908340661341</v>
       </c>
       <c r="L32" s="26"/>
     </row>
@@ -5024,7 +5021,7 @@
       </c>
       <c r="K40" s="28">
         <f>IFERROR(J40/$J$51,0)</f>
-        <v>6.8520912925503719E-2</v>
+        <v>6.6717906328484761E-2</v>
       </c>
       <c r="L40" s="26"/>
     </row>
@@ -5271,7 +5268,7 @@
       </c>
       <c r="K48" s="28">
         <f>IFERROR(J48/$J$51,0)</f>
-        <v>1.3173619086357637E-2</v>
+        <v>1.2826978606754847E-2</v>
       </c>
       <c r="L48" s="26"/>
     </row>
@@ -5285,27 +5282,27 @@
       <c r="C50" s="29"/>
       <c r="E50" s="30">
         <f>(E15+E24+E32+E40+E48)*Допущения!$C$17</f>
-        <v>106500</v>
+        <v>112619.3985</v>
       </c>
       <c r="F50" s="30">
         <f>(F15+F24+F32+F40+F48)*Допущения!$C$17</f>
-        <v>277761.48</v>
+        <v>294125.05446000001</v>
       </c>
       <c r="G50" s="30">
         <f>(G15+G24+G32+G40+G48)*Допущения!$C$17</f>
-        <v>754295.43839999998</v>
+        <v>784386.95113679999</v>
       </c>
       <c r="H50" s="30">
         <f>(H15+H24+H32+H40+H48)*Допущения!$C$17</f>
-        <v>1455844.3278719999</v>
+        <v>1492484.3424277438</v>
       </c>
       <c r="I50" s="30">
         <f>(I15+I24+I32+I40+I48)*Допущения!$C$17</f>
-        <v>2194477.9830297595</v>
+        <v>2234679.7267499636</v>
       </c>
       <c r="J50" s="22">
         <f t="shared" ref="J50:J51" si="10">SUM(E50:I50)</f>
-        <v>4788879.229301759</v>
+        <v>4918295.4732745066</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>154</v>
@@ -5318,27 +5315,27 @@
       <c r="C51" s="29"/>
       <c r="E51" s="27">
         <f t="shared" ref="E51:I51" si="11">E15+E24+E32+E40+E48+E50</f>
-        <v>816500</v>
+        <v>863415.3885</v>
       </c>
       <c r="F51" s="27">
         <f t="shared" si="11"/>
-        <v>2129504.6799999997</v>
+        <v>2254958.75086</v>
       </c>
       <c r="G51" s="27">
         <f t="shared" si="11"/>
-        <v>5782931.6944000004</v>
+        <v>6013633.2920488007</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="11"/>
-        <v>11161473.180352001</v>
+        <v>11442379.958612703</v>
       </c>
       <c r="I51" s="27">
         <f t="shared" si="11"/>
-        <v>16824331.203228157</v>
+        <v>17132544.571749721</v>
       </c>
       <c r="J51" s="27">
         <f t="shared" si="10"/>
-        <v>36714740.757980153</v>
+        <v>37706931.96177122</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5394,27 +5391,27 @@
       </c>
       <c r="E54" s="27">
         <f t="shared" ref="E54:I54" si="13">E51+E53</f>
-        <v>1447219.9999999306</v>
+        <v>1494135.3884999305</v>
       </c>
       <c r="F54" s="27">
         <f t="shared" si="13"/>
-        <v>2760224.6799999303</v>
+        <v>2885678.7508599306</v>
       </c>
       <c r="G54" s="27">
         <f t="shared" si="13"/>
-        <v>6413651.6943999305</v>
+        <v>6644353.2920487309</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="13"/>
-        <v>11792193.180351932</v>
+        <v>12073099.958612634</v>
       </c>
       <c r="I54" s="27">
         <f t="shared" si="13"/>
-        <v>17455051.203228086</v>
+        <v>17763264.57174965</v>
       </c>
       <c r="J54" s="27">
         <f t="shared" si="12"/>
-        <v>39868340.75797981</v>
+        <v>40860531.961770877</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5448,27 +5445,27 @@
       </c>
       <c r="E56" s="27">
         <f t="shared" ref="E56:I56" si="14">E54*E55</f>
-        <v>1447219.9999999306</v>
+        <v>1494135.3884999305</v>
       </c>
       <c r="F56" s="27">
         <f t="shared" si="14"/>
-        <v>2300187.2333332752</v>
+        <v>2404732.2923832755</v>
       </c>
       <c r="G56" s="27">
         <f t="shared" si="14"/>
-        <v>4453924.7877777293</v>
+        <v>4614134.2305893963</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="14"/>
-        <v>6824185.8682592195</v>
+        <v>6986747.6612341637</v>
       </c>
       <c r="I56" s="27">
         <f t="shared" si="14"/>
-        <v>8417752.3163715694</v>
+        <v>8566389.1646169219</v>
       </c>
       <c r="J56" s="27">
         <f>SUM(E56:I56)</f>
-        <v>23443270.205741726</v>
+        <v>24066138.737323686</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5491,11 +5488,11 @@
       <c r="B59" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="47">
         <f>J51</f>
-        <v>36714740.757980153</v>
-      </c>
-      <c r="F59" s="36"/>
+        <v>37706931.96177122</v>
+      </c>
+      <c r="F59" s="48"/>
       <c r="L59" s="12" t="s">
         <v>164</v>
       </c>
@@ -5504,11 +5501,11 @@
       <c r="B60" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="47">
         <f>J54</f>
-        <v>39868340.75797981</v>
-      </c>
-      <c r="F60" s="36"/>
+        <v>40860531.961770877</v>
+      </c>
+      <c r="F60" s="48"/>
       <c r="L60" s="12" t="s">
         <v>166</v>
       </c>
@@ -5517,11 +5514,11 @@
       <c r="B61" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="47">
         <f>J56</f>
-        <v>23443270.205741726</v>
-      </c>
-      <c r="F61" s="36"/>
+        <v>24066138.737323686</v>
+      </c>
+      <c r="F61" s="48"/>
       <c r="L61" s="12" t="s">
         <v>168</v>
       </c>
@@ -5530,11 +5527,11 @@
       <c r="B62" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="47">
         <f>J51/5</f>
-        <v>7342948.1515960302</v>
-      </c>
-      <c r="F62" s="36"/>
+        <v>7541386.3923542444</v>
+      </c>
+      <c r="F62" s="48"/>
       <c r="L62" s="12" t="s">
         <v>170</v>
       </c>
@@ -5543,11 +5540,11 @@
       <c r="B63" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="48">
+      <c r="E63" s="47">
         <f>E15/12</f>
-        <v>1275</v>
-      </c>
-      <c r="F63" s="36"/>
+        <v>5391.3325000000004</v>
+      </c>
+      <c r="F63" s="48"/>
       <c r="L63" s="12" t="s">
         <v>172</v>
       </c>
@@ -5560,7 +5557,7 @@
         <f>IF(E15/12&lt;=Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>В бюджете CFO</v>
       </c>
-      <c r="F64" s="36"/>
+      <c r="F64" s="48"/>
       <c r="L64" s="12" t="s">
         <v>174</v>
       </c>
@@ -5569,11 +5566,11 @@
       <c r="B65" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="35">
+      <c r="E65" s="50">
         <f>IFERROR(J51/SUM(Допущения!$C$8:$G$8),0)</f>
-        <v>0.96364148971076513</v>
-      </c>
-      <c r="F65" s="36"/>
+        <v>0.98968325358979581</v>
+      </c>
+      <c r="F65" s="48"/>
       <c r="L65" s="12" t="s">
         <v>176</v>
       </c>
@@ -5582,11 +5579,11 @@
       <c r="B66" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="35">
+      <c r="E66" s="50">
         <f>IFERROR(I51/Допущения!$G$7,0)</f>
-        <v>4.8069517723509021</v>
-      </c>
-      <c r="F66" s="36"/>
+        <v>4.8950127347856345</v>
+      </c>
+      <c r="F66" s="48"/>
       <c r="L66" s="12" t="s">
         <v>178</v>
       </c>
@@ -5595,11 +5592,11 @@
       <c r="B67" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="37">
+      <c r="E67" s="51">
         <f>IFERROR(J51/SUM(Допущения!$C$10:$G$10),0)</f>
-        <v>3.4175501031350787E-2</v>
-      </c>
-      <c r="F67" s="36"/>
+        <v>3.5099070987406888E-2</v>
+      </c>
+      <c r="F67" s="48"/>
       <c r="L67" s="12" t="s">
         <v>180</v>
       </c>
@@ -5608,11 +5605,11 @@
       <c r="B68" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="38">
+      <c r="E68" s="52">
         <f>IFERROR(J15/J51,0)</f>
-        <v>2.2919949388913913E-2</v>
-      </c>
-      <c r="F68" s="36"/>
+        <v>7.9834206777594133E-2</v>
+      </c>
+      <c r="F68" s="48"/>
       <c r="L68" s="12" t="s">
         <v>182</v>
       </c>
@@ -5621,11 +5618,11 @@
       <c r="B69" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="38">
+      <c r="E69" s="52">
         <f>IFERROR(J32/J51,0)</f>
-        <v>0.76162869252786669</v>
-      </c>
-      <c r="F69" s="36"/>
+        <v>0.70824908340661341</v>
+      </c>
+      <c r="F69" s="48"/>
       <c r="L69" s="12" t="s">
         <v>184</v>
       </c>
@@ -5634,71 +5631,71 @@
       <c r="B70" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="38">
+      <c r="E70" s="52">
         <f>IFERROR(J40/J51,0)</f>
-        <v>6.8520912925503719E-2</v>
-      </c>
-      <c r="F70" s="36"/>
+        <v>6.6717906328484761E-2</v>
+      </c>
+      <c r="F70" s="48"/>
       <c r="L70" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="39" t="s">
+      <c r="B72" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="36"/>
+      <c r="L72" s="36"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="40" t="s">
+      <c r="B73" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
-      <c r="L73" s="42"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
+      <c r="L73" s="41"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="43"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="33"/>
-      <c r="L74" s="44"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="43"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="45"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="47"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="45"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="45"/>
+      <c r="L75" s="46"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6735,31 +6732,31 @@
         <v>64</v>
       </c>
       <c r="D7" s="17">
-        <v>12600</v>
+        <v>18525.259999999998</v>
       </c>
       <c r="E7" s="22">
         <f t="array" ref="E7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),1))</f>
-        <v>12600</v>
+        <v>18525.259999999998</v>
       </c>
       <c r="F7" s="22">
         <f t="array" ref="F7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),2))</f>
-        <v>50400</v>
+        <v>74101.039999999994</v>
       </c>
       <c r="G7" s="22">
         <f t="array" ref="G7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),3))</f>
-        <v>126000</v>
+        <v>185252.59999999998</v>
       </c>
       <c r="H7" s="22">
         <f t="array" ref="H7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),4))</f>
-        <v>210000.00000000003</v>
+        <v>308754.33333333331</v>
       </c>
       <c r="I7" s="22">
         <f t="array" ref="I7">IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),5))</f>
-        <v>294000</v>
+        <v>432256.06666666659</v>
       </c>
       <c r="J7" s="22">
         <f t="shared" ref="J7:J14" si="0">SUM(E7:I7)</f>
-        <v>693000</v>
+        <v>1018889.2999999998</v>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="24" t="s">
@@ -6774,31 +6771,31 @@
         <v>64</v>
       </c>
       <c r="D8" s="17">
-        <v>12600</v>
+        <v>27787.9</v>
       </c>
       <c r="E8" s="22">
         <f t="array" ref="E8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),1))</f>
-        <v>12600</v>
+        <v>27787.9</v>
       </c>
       <c r="F8" s="22">
         <f t="array" ref="F8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),2))</f>
-        <v>50400</v>
+        <v>111151.6</v>
       </c>
       <c r="G8" s="22">
         <f t="array" ref="G8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),3))</f>
-        <v>126000</v>
+        <v>277879</v>
       </c>
       <c r="H8" s="22">
         <f t="array" ref="H8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),4))</f>
-        <v>210000.00000000003</v>
+        <v>463131.66666666674</v>
       </c>
       <c r="I8" s="22">
         <f t="array" ref="I8">IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),5))</f>
-        <v>294000</v>
+        <v>648384.33333333337</v>
       </c>
       <c r="J8" s="22">
         <f t="shared" si="0"/>
-        <v>693000</v>
+        <v>1528334.5</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="24" t="s">
@@ -6813,31 +6810,31 @@
         <v>64</v>
       </c>
       <c r="D9" s="17">
-        <v>3360</v>
+        <v>1800</v>
       </c>
       <c r="E9" s="22">
         <f t="array" ref="E9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),1))</f>
-        <v>3360</v>
+        <v>1800</v>
       </c>
       <c r="F9" s="22">
         <f t="array" ref="F9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),2))</f>
-        <v>13440</v>
+        <v>7200</v>
       </c>
       <c r="G9" s="22">
         <f t="array" ref="G9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),3))</f>
-        <v>33600</v>
+        <v>18000</v>
       </c>
       <c r="H9" s="22">
         <f t="array" ref="H9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),4))</f>
-        <v>56000.000000000007</v>
+        <v>30000.000000000004</v>
       </c>
       <c r="I9" s="22">
         <f t="array" ref="I9">IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),5))</f>
-        <v>78400</v>
+        <v>42000</v>
       </c>
       <c r="J9" s="22">
         <f t="shared" si="0"/>
-        <v>184800</v>
+        <v>99000</v>
       </c>
       <c r="K9" s="23"/>
       <c r="L9" s="24" t="s">
@@ -6852,31 +6849,31 @@
         <v>64</v>
       </c>
       <c r="D10" s="17">
-        <v>2940.0000000000005</v>
+        <v>6030</v>
       </c>
       <c r="E10" s="22">
         <f t="array" ref="E10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),1))</f>
-        <v>2940.0000000000005</v>
+        <v>6030</v>
       </c>
       <c r="F10" s="22">
         <f t="array" ref="F10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),2))</f>
-        <v>11760.000000000002</v>
+        <v>24120</v>
       </c>
       <c r="G10" s="22">
         <f t="array" ref="G10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),3))</f>
-        <v>29400.000000000004</v>
+        <v>60300</v>
       </c>
       <c r="H10" s="22">
         <f t="array" ref="H10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),4))</f>
-        <v>49000.000000000015</v>
+        <v>100500</v>
       </c>
       <c r="I10" s="22">
         <f t="array" ref="I10">IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),5))</f>
-        <v>68600</v>
+        <v>140700</v>
       </c>
       <c r="J10" s="22">
         <f t="shared" si="0"/>
-        <v>161700.00000000003</v>
+        <v>331650</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="24" t="s">
@@ -6891,31 +6888,31 @@
         <v>64</v>
       </c>
       <c r="D11" s="17">
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="E11" s="22">
         <f t="array" ref="E11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),1))</f>
-        <v>1260</v>
+        <v>0</v>
       </c>
       <c r="F11" s="22">
         <f t="array" ref="F11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),2))</f>
-        <v>5040</v>
+        <v>0</v>
       </c>
       <c r="G11" s="22">
         <f t="array" ref="G11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),3))</f>
-        <v>12600</v>
+        <v>0</v>
       </c>
       <c r="H11" s="22">
         <f t="array" ref="H11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),4))</f>
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="22">
         <f t="array" ref="I11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),5))</f>
-        <v>29400</v>
+        <v>0</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="0"/>
-        <v>69300</v>
+        <v>0</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="24" t="s">
@@ -6930,31 +6927,31 @@
         <v>64</v>
       </c>
       <c r="D12" s="17">
-        <v>2940.0000000000005</v>
+        <v>11152.83</v>
       </c>
       <c r="E12" s="22">
         <f t="array" ref="E12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),1))</f>
-        <v>2940.0000000000005</v>
+        <v>11152.83</v>
       </c>
       <c r="F12" s="22">
         <f t="array" ref="F12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),2))</f>
-        <v>11760.000000000002</v>
+        <v>44611.32</v>
       </c>
       <c r="G12" s="22">
         <f t="array" ref="G12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),3))</f>
-        <v>29400.000000000004</v>
+        <v>111528.3</v>
       </c>
       <c r="H12" s="22">
         <f t="array" ref="H12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),4))</f>
-        <v>49000.000000000015</v>
+        <v>185880.5</v>
       </c>
       <c r="I12" s="22">
         <f t="array" ref="I12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),5))</f>
-        <v>68600</v>
+        <v>260232.69999999998</v>
       </c>
       <c r="J12" s="22">
         <f t="shared" si="0"/>
-        <v>161700.00000000003</v>
+        <v>613405.65</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="24" t="s">
@@ -7045,31 +7042,31 @@
       <c r="D15" s="26"/>
       <c r="E15" s="27">
         <f t="shared" ref="E15:J15" si="1">SUM(E7:E14)</f>
-        <v>35700</v>
+        <v>65295.990000000005</v>
       </c>
       <c r="F15" s="27">
         <f t="shared" si="1"/>
-        <v>142800</v>
+        <v>261183.96000000002</v>
       </c>
       <c r="G15" s="27">
         <f t="shared" si="1"/>
-        <v>357000</v>
+        <v>652959.9</v>
       </c>
       <c r="H15" s="27">
         <f t="shared" si="1"/>
-        <v>595000.00000000012</v>
+        <v>1088266.5</v>
       </c>
       <c r="I15" s="27">
         <f t="shared" si="1"/>
-        <v>833000</v>
+        <v>1523573.0999999999</v>
       </c>
       <c r="J15" s="27">
         <f t="shared" si="1"/>
-        <v>1963500</v>
+        <v>3591279.4499999997</v>
       </c>
       <c r="K15" s="28">
         <f>IFERROR(J15/$J$51,0)</f>
-        <v>5.0051298771306874E-2</v>
+        <v>9.102274974229374E-2</v>
       </c>
       <c r="L15" s="26"/>
     </row>
@@ -7099,31 +7096,31 @@
         <v>64</v>
       </c>
       <c r="D18" s="17">
-        <v>3360</v>
+        <v>1800</v>
       </c>
       <c r="E18" s="22">
         <f t="array" ref="E18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),1))</f>
-        <v>3360</v>
+        <v>1800</v>
       </c>
       <c r="F18" s="22">
         <f t="array" ref="F18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),2))</f>
-        <v>13440</v>
+        <v>7200</v>
       </c>
       <c r="G18" s="22">
         <f t="array" ref="G18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),3))</f>
-        <v>33600</v>
+        <v>18000</v>
       </c>
       <c r="H18" s="22">
         <f t="array" ref="H18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),4))</f>
-        <v>56000.000000000007</v>
+        <v>30000.000000000004</v>
       </c>
       <c r="I18" s="22">
         <f t="array" ref="I18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),5))</f>
-        <v>78400</v>
+        <v>42000</v>
       </c>
       <c r="J18" s="22">
         <f t="shared" ref="J18:J23" si="2">SUM(E18:I18)</f>
-        <v>184800</v>
+        <v>99000</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="24" t="s">
@@ -7138,31 +7135,31 @@
         <v>90</v>
       </c>
       <c r="D19" s="17">
-        <v>1260</v>
+        <v>1200</v>
       </c>
       <c r="E19" s="22">
         <f t="array" ref="E19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),1))</f>
-        <v>1260</v>
+        <v>1200</v>
       </c>
       <c r="F19" s="22">
         <f t="array" ref="F19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),2))</f>
-        <v>1360.8000000000002</v>
+        <v>1296</v>
       </c>
       <c r="G19" s="22">
         <f t="array" ref="G19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),3))</f>
-        <v>1469.6640000000002</v>
+        <v>1399.68</v>
       </c>
       <c r="H19" s="22">
         <f t="array" ref="H19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),4))</f>
-        <v>1587.2371200000002</v>
+        <v>1511.6544000000001</v>
       </c>
       <c r="I19" s="22">
         <f t="array" ref="I19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),5))</f>
-        <v>1714.2160896000005</v>
+        <v>1632.5867520000004</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="2"/>
-        <v>7391.9172096000011</v>
+        <v>7039.9211520000008</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="24" t="s">
@@ -7177,31 +7174,31 @@
         <v>64</v>
       </c>
       <c r="D20" s="17">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="E20" s="22">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),1))</f>
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="F20" s="22">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),2))</f>
-        <v>6720</v>
+        <v>0</v>
       </c>
       <c r="G20" s="22">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),3))</f>
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="H20" s="22">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),4))</f>
-        <v>28000.000000000004</v>
+        <v>0</v>
       </c>
       <c r="I20" s="22">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),5))</f>
-        <v>39200</v>
+        <v>0</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="2"/>
-        <v>92400</v>
+        <v>0</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="24" t="s">
@@ -7216,31 +7213,31 @@
         <v>90</v>
       </c>
       <c r="D21" s="17">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E21" s="22">
         <f t="array" ref="E21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F21" s="22">
         <f t="array" ref="F21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="G21" s="22">
         <f t="array" ref="G21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>699.84</v>
       </c>
       <c r="H21" s="22">
         <f t="array" ref="H21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>755.82720000000006</v>
       </c>
       <c r="I21" s="22">
         <f t="array" ref="I21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>816.29337600000019</v>
       </c>
       <c r="J21" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3519.9605760000004</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="24" t="s">
@@ -7331,31 +7328,31 @@
       <c r="D24" s="26"/>
       <c r="E24" s="27">
         <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
-        <v>6300</v>
+        <v>3600</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" si="3"/>
-        <v>21520.799999999999</v>
+        <v>9144</v>
       </c>
       <c r="G24" s="27">
         <f t="shared" si="3"/>
-        <v>51869.663999999997</v>
+        <v>20099.52</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="3"/>
-        <v>85587.237120000005</v>
+        <v>32267.481600000003</v>
       </c>
       <c r="I24" s="27">
         <f t="shared" si="3"/>
-        <v>119314.2160896</v>
+        <v>44448.880128000004</v>
       </c>
       <c r="J24" s="27">
         <f t="shared" si="3"/>
-        <v>284591.91720959998</v>
+        <v>109559.88172799999</v>
       </c>
       <c r="K24" s="28">
         <f>IFERROR(J24/$J$51,0)</f>
-        <v>7.2544920173958334E-3</v>
+        <v>2.7768492636581219E-3</v>
       </c>
       <c r="L24" s="26"/>
     </row>
@@ -7385,32 +7382,31 @@
         <v>97</v>
       </c>
       <c r="D27" s="17">
-        <f>Допущения!C10*0.02</f>
-        <v>150000</v>
+        <v>137500</v>
       </c>
       <c r="E27" s="22">
         <f t="array" ref="E27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),1))</f>
-        <v>150000</v>
+        <v>137500</v>
       </c>
       <c r="F27" s="22">
         <f t="array" ref="F27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),2))</f>
-        <v>936000</v>
+        <v>858000</v>
       </c>
       <c r="G27" s="22">
         <f t="array" ref="G27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),3))</f>
-        <v>3240000</v>
+        <v>2970000</v>
       </c>
       <c r="H27" s="22">
         <f t="array" ref="H27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),4))</f>
-        <v>6720000</v>
+        <v>6160000</v>
       </c>
       <c r="I27" s="22">
         <f t="array" ref="I27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),5))</f>
-        <v>10440000</v>
+        <v>9570000</v>
       </c>
       <c r="J27" s="22">
         <f t="shared" ref="J27:J31" si="4">SUM(E27:I27)</f>
-        <v>21486000</v>
+        <v>19695500</v>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="24" t="s">
@@ -7425,32 +7421,31 @@
         <v>95</v>
       </c>
       <c r="D28" s="17">
-        <f>Допущения!C8*0.05</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E28" s="22">
         <f t="array" ref="E28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),1))</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="F28" s="22">
         <f t="array" ref="F28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),2))</f>
-        <v>90000</v>
+        <v>108000</v>
       </c>
       <c r="G28" s="22">
         <f t="array" ref="G28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),3))</f>
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="H28" s="22">
         <f t="array" ref="H28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),4))</f>
-        <v>600000</v>
+        <v>720000</v>
       </c>
       <c r="I28" s="22">
         <f t="array" ref="I28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),5))</f>
-        <v>900000</v>
+        <v>1080000</v>
       </c>
       <c r="J28" s="22">
         <f t="shared" si="4"/>
-        <v>1905000</v>
+        <v>2286000</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="24" t="s">
@@ -7465,32 +7460,31 @@
         <v>95</v>
       </c>
       <c r="D29" s="17">
-        <f>Допущения!C8*0.02</f>
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="E29" s="22">
         <f t="array" ref="E29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),1))</f>
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="F29" s="22">
         <f t="array" ref="F29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),2))</f>
-        <v>36000</v>
+        <v>43200</v>
       </c>
       <c r="G29" s="22">
         <f t="array" ref="G29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),3))</f>
-        <v>120000</v>
+        <v>144000</v>
       </c>
       <c r="H29" s="22">
         <f t="array" ref="H29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),4))</f>
-        <v>240000</v>
+        <v>288000</v>
       </c>
       <c r="I29" s="22">
         <f t="array" ref="I29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),5))</f>
-        <v>360000</v>
+        <v>432000</v>
       </c>
       <c r="J29" s="22">
         <f t="shared" si="4"/>
-        <v>762000</v>
+        <v>914400</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="24" t="s">
@@ -7582,31 +7576,31 @@
       <c r="D32" s="26"/>
       <c r="E32" s="27">
         <f t="shared" ref="E32:J32" si="5">SUM(E27:E31)</f>
-        <v>201000</v>
+        <v>192700</v>
       </c>
       <c r="F32" s="27">
         <f t="shared" si="5"/>
-        <v>1242000</v>
+        <v>1189200</v>
       </c>
       <c r="G32" s="27">
         <f t="shared" si="5"/>
-        <v>4260000</v>
+        <v>4074000</v>
       </c>
       <c r="H32" s="27">
         <f t="shared" si="5"/>
-        <v>8760000</v>
+        <v>8368000</v>
       </c>
       <c r="I32" s="27">
         <f t="shared" si="5"/>
-        <v>13500000</v>
+        <v>12882000</v>
       </c>
       <c r="J32" s="27">
         <f t="shared" si="5"/>
-        <v>27963000</v>
+        <v>26705900</v>
       </c>
       <c r="K32" s="28">
         <f>IFERROR(J32/$J$51,0)</f>
-        <v>0.71280084927020826</v>
+        <v>0.67687421326756469</v>
       </c>
       <c r="L32" s="26"/>
     </row>
@@ -7853,7 +7847,7 @@
       </c>
       <c r="K40" s="28">
         <f>IFERROR(J40/$J$51,0)</f>
-        <v>8.3560795931833964E-2</v>
+        <v>8.3084282362526865E-2</v>
       </c>
       <c r="L40" s="26"/>
     </row>
@@ -8100,7 +8094,7 @@
       </c>
       <c r="K48" s="28">
         <f>IFERROR(J48/$J$51,0)</f>
-        <v>1.5897781400559377E-2</v>
+        <v>1.5807122755260878E-2</v>
       </c>
       <c r="L48" s="26"/>
     </row>
@@ -8114,27 +8108,27 @@
       <c r="C50" s="29"/>
       <c r="E50" s="30">
         <f>(E15+E24+E32+E40+E48)*Допущения!$C$17</f>
-        <v>132300</v>
+        <v>135089.39849999998</v>
       </c>
       <c r="F50" s="30">
         <f>(F15+F24+F32+F40+F48)*Допущения!$C$17</f>
-        <v>316206.11999999994</v>
+        <v>324187.19399999996</v>
       </c>
       <c r="G50" s="30">
         <f>(G15+G24+G32+G40+G48)*Допущения!$C$17</f>
-        <v>816120.60959999997</v>
+        <v>827849.07299999997</v>
       </c>
       <c r="H50" s="30">
         <f>(H15+H24+H32+H40+H48)*Допущения!$C$17</f>
-        <v>1543669.0807679999</v>
+        <v>1550861.0924399996</v>
       </c>
       <c r="I50" s="30">
         <f>(I15+I24+I32+I40+I48)*Допущения!$C$17</f>
-        <v>2308628.2643174399</v>
+        <v>2308284.4289231999</v>
       </c>
       <c r="J50" s="22">
         <f t="shared" ref="J50:J51" si="10">SUM(E50:I50)</f>
-        <v>5116924.0746854395</v>
+        <v>5146271.1868631989</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>154</v>
@@ -8147,27 +8141,27 @@
       <c r="C51" s="29"/>
       <c r="E51" s="27">
         <f t="shared" ref="E51:I51" si="11">E15+E24+E32+E40+E48+E50</f>
-        <v>1014300</v>
+        <v>1035685.3885</v>
       </c>
       <c r="F51" s="27">
         <f t="shared" si="11"/>
-        <v>2424246.92</v>
+        <v>2485435.1540000001</v>
       </c>
       <c r="G51" s="27">
         <f t="shared" si="11"/>
-        <v>6256924.6736000003</v>
+        <v>6346842.8930000002</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="11"/>
-        <v>11834796.285887999</v>
+        <v>11889935.042039998</v>
       </c>
       <c r="I51" s="27">
         <f t="shared" si="11"/>
-        <v>17699483.359767042</v>
+        <v>17696847.2884112</v>
       </c>
       <c r="J51" s="27">
         <f t="shared" si="10"/>
-        <v>39229751.239255041</v>
+        <v>39454745.765951201</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8223,27 +8217,27 @@
       </c>
       <c r="E54" s="27">
         <f t="shared" ref="E54:I54" si="13">E51+E53</f>
-        <v>1645019.9999999306</v>
+        <v>1666405.3884999305</v>
       </c>
       <c r="F54" s="27">
         <f t="shared" si="13"/>
-        <v>3054966.9199999305</v>
+        <v>3116155.1539999307</v>
       </c>
       <c r="G54" s="27">
         <f t="shared" si="13"/>
-        <v>6887644.6735999305</v>
+        <v>6977562.8929999303</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="13"/>
-        <v>12465516.285887931</v>
+        <v>12520655.042039929</v>
       </c>
       <c r="I54" s="27">
         <f t="shared" si="13"/>
-        <v>18330203.359766971</v>
+        <v>18327567.288411129</v>
       </c>
       <c r="J54" s="27">
         <f t="shared" si="12"/>
-        <v>42383351.239254698</v>
+        <v>42608345.765950844</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8277,27 +8271,27 @@
       </c>
       <c r="E56" s="27">
         <f t="shared" ref="E56:I56" si="14">E54*E55</f>
-        <v>1645019.9999999306</v>
+        <v>1666405.3884999305</v>
       </c>
       <c r="F56" s="27">
         <f t="shared" si="14"/>
-        <v>2545805.7666666089</v>
+        <v>2596795.9616666092</v>
       </c>
       <c r="G56" s="27">
         <f t="shared" si="14"/>
-        <v>4783086.57888884</v>
+        <v>4845529.7868055068</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="14"/>
-        <v>7213840.4432221819</v>
+        <v>7245749.4456249587</v>
       </c>
       <c r="I56" s="27">
         <f t="shared" si="14"/>
-        <v>8839797.1449493505</v>
+        <v>8838525.8914019726</v>
       </c>
       <c r="J56" s="27">
         <f>SUM(E56:I56)</f>
-        <v>25027549.933726914</v>
+        <v>25193006.473998979</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8320,11 +8314,11 @@
       <c r="B59" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="47">
         <f>J51</f>
-        <v>39229751.239255041</v>
-      </c>
-      <c r="F59" s="36"/>
+        <v>39454745.765951201</v>
+      </c>
+      <c r="F59" s="48"/>
       <c r="L59" s="12" t="s">
         <v>164</v>
       </c>
@@ -8333,11 +8327,11 @@
       <c r="B60" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="47">
         <f>J54</f>
-        <v>42383351.239254698</v>
-      </c>
-      <c r="F60" s="36"/>
+        <v>42608345.765950844</v>
+      </c>
+      <c r="F60" s="48"/>
       <c r="L60" s="12" t="s">
         <v>166</v>
       </c>
@@ -8346,11 +8340,11 @@
       <c r="B61" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="47">
         <f>J56</f>
-        <v>25027549.933726914</v>
-      </c>
-      <c r="F61" s="36"/>
+        <v>25193006.473998979</v>
+      </c>
+      <c r="F61" s="48"/>
       <c r="L61" s="12" t="s">
         <v>168</v>
       </c>
@@ -8359,11 +8353,11 @@
       <c r="B62" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="47">
         <f>J51/5</f>
-        <v>7845950.2478510085</v>
-      </c>
-      <c r="F62" s="36"/>
+        <v>7890949.1531902403</v>
+      </c>
+      <c r="F62" s="48"/>
       <c r="L62" s="12" t="s">
         <v>170</v>
       </c>
@@ -8372,11 +8366,11 @@
       <c r="B63" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="48">
+      <c r="E63" s="47">
         <f>E15/12</f>
-        <v>2975</v>
-      </c>
-      <c r="F63" s="36"/>
+        <v>5441.3325000000004</v>
+      </c>
+      <c r="F63" s="48"/>
       <c r="L63" s="12" t="s">
         <v>172</v>
       </c>
@@ -8389,7 +8383,7 @@
         <f>IF(E15/12&lt;=Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>В бюджете CFO</v>
       </c>
-      <c r="F64" s="36"/>
+      <c r="F64" s="48"/>
       <c r="L64" s="12" t="s">
         <v>174</v>
       </c>
@@ -8398,11 +8392,11 @@
       <c r="B65" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="35">
+      <c r="E65" s="50">
         <f>IFERROR(J51/SUM(Допущения!$C$8:$G$8),0)</f>
-        <v>1.0296522634975076</v>
-      </c>
-      <c r="F65" s="36"/>
+        <v>1.0355576316522626</v>
+      </c>
+      <c r="F65" s="48"/>
       <c r="L65" s="12" t="s">
         <v>176</v>
       </c>
@@ -8411,11 +8405,11 @@
       <c r="B66" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="35">
+      <c r="E66" s="50">
         <f>IFERROR(I51/Допущения!$G$7,0)</f>
-        <v>5.0569952456477267</v>
-      </c>
-      <c r="F66" s="36"/>
+        <v>5.0562420824031999</v>
+      </c>
+      <c r="F66" s="48"/>
       <c r="L66" s="12" t="s">
         <v>178</v>
       </c>
@@ -8424,11 +8418,11 @@
       <c r="B67" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="37">
+      <c r="E67" s="51">
         <f>IFERROR(J51/SUM(Допущения!$C$10:$G$10),0)</f>
-        <v>3.6516570082151208E-2</v>
-      </c>
-      <c r="F67" s="36"/>
+        <v>3.6726003691660805E-2</v>
+      </c>
+      <c r="F67" s="48"/>
       <c r="L67" s="12" t="s">
         <v>180</v>
       </c>
@@ -8437,11 +8431,11 @@
       <c r="B68" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="38">
+      <c r="E68" s="52">
         <f>IFERROR(J15/J51,0)</f>
-        <v>5.0051298771306874E-2</v>
-      </c>
-      <c r="F68" s="36"/>
+        <v>9.102274974229374E-2</v>
+      </c>
+      <c r="F68" s="48"/>
       <c r="L68" s="12" t="s">
         <v>182</v>
       </c>
@@ -8450,11 +8444,11 @@
       <c r="B69" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="38">
+      <c r="E69" s="52">
         <f>IFERROR(J32/J51,0)</f>
-        <v>0.71280084927020826</v>
-      </c>
-      <c r="F69" s="36"/>
+        <v>0.67687421326756469</v>
+      </c>
+      <c r="F69" s="48"/>
       <c r="L69" s="12" t="s">
         <v>184</v>
       </c>
@@ -8463,71 +8457,71 @@
       <c r="B70" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="38">
+      <c r="E70" s="52">
         <f>IFERROR(J40/J51,0)</f>
-        <v>8.3560795931833964E-2</v>
-      </c>
-      <c r="F70" s="36"/>
+        <v>8.3084282362526865E-2</v>
+      </c>
+      <c r="F70" s="48"/>
       <c r="L70" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="39" t="s">
+      <c r="B72" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="36"/>
+      <c r="L72" s="36"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="40" t="s">
+      <c r="B73" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
-      <c r="L73" s="42"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
+      <c r="L73" s="41"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="43"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="33"/>
-      <c r="L74" s="44"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="43"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="45"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="47"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="45"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="45"/>
+      <c r="L75" s="46"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9720,31 +9714,31 @@
         <v>64</v>
       </c>
       <c r="D11" s="17">
-        <v>6480</v>
+        <v>0</v>
       </c>
       <c r="E11" s="22">
         <f t="array" ref="E11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),1))</f>
-        <v>6480</v>
+        <v>0</v>
       </c>
       <c r="F11" s="22">
         <f t="array" ref="F11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),2))</f>
-        <v>25920</v>
+        <v>0</v>
       </c>
       <c r="G11" s="22">
         <f t="array" ref="G11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),3))</f>
-        <v>64800</v>
+        <v>0</v>
       </c>
       <c r="H11" s="22">
         <f t="array" ref="H11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),4))</f>
-        <v>108000.00000000001</v>
+        <v>0</v>
       </c>
       <c r="I11" s="22">
         <f t="array" ref="I11">IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),5))</f>
-        <v>151200</v>
+        <v>0</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="0"/>
-        <v>356400</v>
+        <v>0</v>
       </c>
       <c r="K11" s="23"/>
       <c r="L11" s="24" t="s">
@@ -9759,31 +9753,31 @@
         <v>64</v>
       </c>
       <c r="D12" s="17">
-        <v>15120.000000000002</v>
+        <v>0</v>
       </c>
       <c r="E12" s="22">
         <f t="array" ref="E12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),1))</f>
-        <v>15120.000000000002</v>
+        <v>0</v>
       </c>
       <c r="F12" s="22">
         <f t="array" ref="F12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),2))</f>
-        <v>60480.000000000007</v>
+        <v>0</v>
       </c>
       <c r="G12" s="22">
         <f t="array" ref="G12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),3))</f>
-        <v>151200.00000000003</v>
+        <v>0</v>
       </c>
       <c r="H12" s="22">
         <f t="array" ref="H12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),4))</f>
-        <v>252000.00000000006</v>
+        <v>0</v>
       </c>
       <c r="I12" s="22">
         <f t="array" ref="I12">IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),5))</f>
-        <v>352800</v>
+        <v>0</v>
       </c>
       <c r="J12" s="22">
         <f t="shared" si="0"/>
-        <v>831600.00000000012</v>
+        <v>0</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="24" t="s">
@@ -9798,31 +9792,31 @@
         <v>90</v>
       </c>
       <c r="D13" s="17">
-        <v>0</v>
+        <v>11152.83</v>
       </c>
       <c r="E13" s="22">
         <f t="array" ref="E13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>11152.83</v>
       </c>
       <c r="F13" s="22">
         <f t="array" ref="F13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>12045.056400000001</v>
       </c>
       <c r="G13" s="22">
         <f t="array" ref="G13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>13008.660912000001</v>
       </c>
       <c r="H13" s="22">
         <f t="array" ref="H13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>14049.353784960002</v>
       </c>
       <c r="I13" s="22">
         <f t="array" ref="I13">IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>15173.302087756803</v>
       </c>
       <c r="J13" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>65429.203184716811</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="24" t="s">
@@ -9874,31 +9868,31 @@
       <c r="D15" s="26"/>
       <c r="E15" s="27">
         <f t="shared" ref="E15:J15" si="1">SUM(E7:E14)</f>
-        <v>183600</v>
+        <v>173152.83</v>
       </c>
       <c r="F15" s="27">
         <f t="shared" si="1"/>
-        <v>734400</v>
+        <v>660045.0564</v>
       </c>
       <c r="G15" s="27">
         <f t="shared" si="1"/>
-        <v>1836000</v>
+        <v>1633008.6609120001</v>
       </c>
       <c r="H15" s="27">
         <f t="shared" si="1"/>
-        <v>3060000</v>
+        <v>2714049.3537849602</v>
       </c>
       <c r="I15" s="27">
         <f t="shared" si="1"/>
-        <v>4284000</v>
+        <v>3795173.3020877568</v>
       </c>
       <c r="J15" s="27">
         <f t="shared" si="1"/>
-        <v>10098000</v>
+        <v>8975429.2031847164</v>
       </c>
       <c r="K15" s="28">
         <f>IFERROR(J15/$J$51,0)</f>
-        <v>0.18711617424965674</v>
+        <v>0.17997947908845238</v>
       </c>
       <c r="L15" s="26"/>
     </row>
@@ -9928,31 +9922,31 @@
         <v>64</v>
       </c>
       <c r="D18" s="17">
-        <v>17280</v>
+        <v>0</v>
       </c>
       <c r="E18" s="22">
         <f t="array" ref="E18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),1))</f>
-        <v>17280</v>
+        <v>0</v>
       </c>
       <c r="F18" s="22">
         <f t="array" ref="F18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),2))</f>
-        <v>69120</v>
+        <v>0</v>
       </c>
       <c r="G18" s="22">
         <f t="array" ref="G18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),3))</f>
-        <v>172800</v>
+        <v>0</v>
       </c>
       <c r="H18" s="22">
         <f t="array" ref="H18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),4))</f>
-        <v>288000</v>
+        <v>0</v>
       </c>
       <c r="I18" s="22">
         <f t="array" ref="I18">IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),5))</f>
-        <v>403200</v>
+        <v>0</v>
       </c>
       <c r="J18" s="22">
         <f t="shared" ref="J18:J23" si="2">SUM(E18:I18)</f>
-        <v>950400</v>
+        <v>0</v>
       </c>
       <c r="K18" s="23"/>
       <c r="L18" s="24" t="s">
@@ -9967,31 +9961,31 @@
         <v>90</v>
       </c>
       <c r="D19" s="17">
-        <v>6480</v>
+        <v>0</v>
       </c>
       <c r="E19" s="22">
         <f t="array" ref="E19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),1))</f>
-        <v>6480</v>
+        <v>0</v>
       </c>
       <c r="F19" s="22">
         <f t="array" ref="F19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),2))</f>
-        <v>6998.4000000000005</v>
+        <v>0</v>
       </c>
       <c r="G19" s="22">
         <f t="array" ref="G19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),3))</f>
-        <v>7558.2720000000008</v>
+        <v>0</v>
       </c>
       <c r="H19" s="22">
         <f t="array" ref="H19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),4))</f>
-        <v>8162.9337600000008</v>
+        <v>0</v>
       </c>
       <c r="I19" s="22">
         <f t="array" ref="I19">IF($D19="","",$D19*INDEX(Допущения!$C$25:$G$30,MATCH($C19,Допущения!$B$25:$B$30,0),5))</f>
-        <v>8815.9684608000025</v>
+        <v>0</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="2"/>
-        <v>38015.574220800001</v>
+        <v>0</v>
       </c>
       <c r="K19" s="23"/>
       <c r="L19" s="24" t="s">
@@ -10006,31 +10000,31 @@
         <v>64</v>
       </c>
       <c r="D20" s="17">
-        <v>8640</v>
+        <v>0</v>
       </c>
       <c r="E20" s="22">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),1))</f>
-        <v>8640</v>
+        <v>0</v>
       </c>
       <c r="F20" s="22">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),2))</f>
-        <v>34560</v>
+        <v>0</v>
       </c>
       <c r="G20" s="22">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),3))</f>
-        <v>86400</v>
+        <v>0</v>
       </c>
       <c r="H20" s="22">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),4))</f>
-        <v>144000</v>
+        <v>0</v>
       </c>
       <c r="I20" s="22">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),5))</f>
-        <v>201600</v>
+        <v>0</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="2"/>
-        <v>475200</v>
+        <v>0</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="24" t="s">
@@ -10045,31 +10039,31 @@
         <v>90</v>
       </c>
       <c r="D21" s="17">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E21" s="22">
         <f t="array" ref="E21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F21" s="22">
         <f t="array" ref="F21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="G21" s="22">
         <f t="array" ref="G21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>699.84</v>
       </c>
       <c r="H21" s="22">
         <f t="array" ref="H21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>755.82720000000006</v>
       </c>
       <c r="I21" s="22">
         <f t="array" ref="I21">IF($D21="","",$D21*INDEX(Допущения!$C$25:$G$30,MATCH($C21,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>816.29337600000019</v>
       </c>
       <c r="J21" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3519.9605760000004</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="24" t="s">
@@ -10084,31 +10078,31 @@
         <v>90</v>
       </c>
       <c r="D22" s="17">
-        <v>120000</v>
+        <v>167200</v>
       </c>
       <c r="E22" s="22">
         <f t="array" ref="E22">IF($D22="","",$D22*INDEX(Допущения!$C$25:$G$30,MATCH($C22,Допущения!$B$25:$B$30,0),1))</f>
-        <v>120000</v>
+        <v>167200</v>
       </c>
       <c r="F22" s="22">
         <f t="array" ref="F22">IF($D22="","",$D22*INDEX(Допущения!$C$25:$G$30,MATCH($C22,Допущения!$B$25:$B$30,0),2))</f>
-        <v>129600.00000000001</v>
+        <v>180576</v>
       </c>
       <c r="G22" s="22">
         <f t="array" ref="G22">IF($D22="","",$D22*INDEX(Допущения!$C$25:$G$30,MATCH($C22,Допущения!$B$25:$B$30,0),3))</f>
-        <v>139968</v>
+        <v>195022.08000000002</v>
       </c>
       <c r="H22" s="22">
         <f t="array" ref="H22">IF($D22="","",$D22*INDEX(Допущения!$C$25:$G$30,MATCH($C22,Допущения!$B$25:$B$30,0),4))</f>
-        <v>151165.44000000003</v>
+        <v>210623.84640000004</v>
       </c>
       <c r="I22" s="22">
         <f t="array" ref="I22">IF($D22="","",$D22*INDEX(Допущения!$C$25:$G$30,MATCH($C22,Допущения!$B$25:$B$30,0),5))</f>
-        <v>163258.67520000003</v>
+        <v>227473.75411200005</v>
       </c>
       <c r="J22" s="22">
         <f t="shared" si="2"/>
-        <v>703992.11520000012</v>
+        <v>980895.68051200011</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="24" t="s">
@@ -10160,31 +10154,31 @@
       <c r="D24" s="26"/>
       <c r="E24" s="27">
         <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
-        <v>152400</v>
+        <v>167800</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" si="3"/>
-        <v>240278.40000000002</v>
+        <v>181224</v>
       </c>
       <c r="G24" s="27">
         <f t="shared" si="3"/>
-        <v>406726.272</v>
+        <v>195721.92</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="3"/>
-        <v>591328.37375999999</v>
+        <v>211379.67360000004</v>
       </c>
       <c r="I24" s="27">
         <f t="shared" si="3"/>
-        <v>776874.64366080007</v>
+        <v>228290.04748800004</v>
       </c>
       <c r="J24" s="27">
         <f t="shared" si="3"/>
-        <v>2167607.6894207997</v>
+        <v>984415.64108800015</v>
       </c>
       <c r="K24" s="28">
         <f>IFERROR(J24/$J$51,0)</f>
-        <v>4.016582076832622E-2</v>
+        <v>1.9739960093125911E-2</v>
       </c>
       <c r="L24" s="26"/>
     </row>
@@ -10214,32 +10208,31 @@
         <v>97</v>
       </c>
       <c r="D27" s="17">
-        <f>Допущения!C10*0.02</f>
-        <v>150000</v>
+        <v>137500</v>
       </c>
       <c r="E27" s="22">
         <f t="array" ref="E27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),1))</f>
-        <v>150000</v>
+        <v>137500</v>
       </c>
       <c r="F27" s="22">
         <f t="array" ref="F27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),2))</f>
-        <v>936000</v>
+        <v>858000</v>
       </c>
       <c r="G27" s="22">
         <f t="array" ref="G27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),3))</f>
-        <v>3240000</v>
+        <v>2970000</v>
       </c>
       <c r="H27" s="22">
         <f t="array" ref="H27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),4))</f>
-        <v>6720000</v>
+        <v>6160000</v>
       </c>
       <c r="I27" s="22">
         <f t="array" ref="I27">IF($D27="","",$D27*INDEX(Допущения!$C$25:$G$30,MATCH($C27,Допущения!$B$25:$B$30,0),5))</f>
-        <v>10440000</v>
+        <v>9570000</v>
       </c>
       <c r="J27" s="22">
         <f t="shared" ref="J27:J31" si="4">SUM(E27:I27)</f>
-        <v>21486000</v>
+        <v>19695500</v>
       </c>
       <c r="K27" s="23"/>
       <c r="L27" s="24" t="s">
@@ -10254,32 +10247,31 @@
         <v>95</v>
       </c>
       <c r="D28" s="17">
-        <f>Допущения!C8*0.05</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E28" s="22">
         <f t="array" ref="E28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),1))</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="F28" s="22">
         <f t="array" ref="F28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),2))</f>
-        <v>90000</v>
+        <v>108000</v>
       </c>
       <c r="G28" s="22">
         <f t="array" ref="G28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),3))</f>
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="H28" s="22">
         <f t="array" ref="H28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),4))</f>
-        <v>600000</v>
+        <v>720000</v>
       </c>
       <c r="I28" s="22">
         <f t="array" ref="I28">IF($D28="","",$D28*INDEX(Допущения!$C$25:$G$30,MATCH($C28,Допущения!$B$25:$B$30,0),5))</f>
-        <v>900000</v>
+        <v>1080000</v>
       </c>
       <c r="J28" s="22">
         <f t="shared" si="4"/>
-        <v>1905000</v>
+        <v>2286000</v>
       </c>
       <c r="K28" s="23"/>
       <c r="L28" s="24" t="s">
@@ -10294,32 +10286,31 @@
         <v>95</v>
       </c>
       <c r="D29" s="17">
-        <f>Допущения!C8*0.02</f>
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="E29" s="22">
         <f t="array" ref="E29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),1))</f>
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="F29" s="22">
         <f t="array" ref="F29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),2))</f>
-        <v>36000</v>
+        <v>43200</v>
       </c>
       <c r="G29" s="22">
         <f t="array" ref="G29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),3))</f>
-        <v>120000</v>
+        <v>144000</v>
       </c>
       <c r="H29" s="22">
         <f t="array" ref="H29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),4))</f>
-        <v>240000</v>
+        <v>288000</v>
       </c>
       <c r="I29" s="22">
         <f t="array" ref="I29">IF($D29="","",$D29*INDEX(Допущения!$C$25:$G$30,MATCH($C29,Допущения!$B$25:$B$30,0),5))</f>
-        <v>360000</v>
+        <v>432000</v>
       </c>
       <c r="J29" s="22">
         <f t="shared" si="4"/>
-        <v>762000</v>
+        <v>914400</v>
       </c>
       <c r="K29" s="23"/>
       <c r="L29" s="24" t="s">
@@ -10411,31 +10402,31 @@
       <c r="D32" s="26"/>
       <c r="E32" s="27">
         <f t="shared" ref="E32:J32" si="5">SUM(E27:E31)</f>
-        <v>201000</v>
+        <v>192700</v>
       </c>
       <c r="F32" s="27">
         <f t="shared" si="5"/>
-        <v>1242000</v>
+        <v>1189200</v>
       </c>
       <c r="G32" s="27">
         <f t="shared" si="5"/>
-        <v>4260000</v>
+        <v>4074000</v>
       </c>
       <c r="H32" s="27">
         <f t="shared" si="5"/>
-        <v>8760000</v>
+        <v>8368000</v>
       </c>
       <c r="I32" s="27">
         <f t="shared" si="5"/>
-        <v>13500000</v>
+        <v>12882000</v>
       </c>
       <c r="J32" s="27">
         <f t="shared" si="5"/>
-        <v>27963000</v>
+        <v>26705900</v>
       </c>
       <c r="K32" s="28">
         <f>IFERROR(J32/$J$51,0)</f>
-        <v>0.51815503867529722</v>
+        <v>0.53551912245966182</v>
       </c>
       <c r="L32" s="26"/>
     </row>
@@ -10682,7 +10673,7 @@
       </c>
       <c r="K40" s="28">
         <f>IFERROR(J40/$J$51,0)</f>
-        <v>0.10312132624177295</v>
+        <v>0.11159385788055466</v>
       </c>
       <c r="L40" s="26"/>
     </row>
@@ -10929,7 +10920,7 @@
       </c>
       <c r="K48" s="28">
         <f>IFERROR(J48/$J$51,0)</f>
-        <v>2.1006857456251398E-2</v>
+        <v>2.2732797869509679E-2</v>
       </c>
       <c r="L48" s="26"/>
     </row>
@@ -10943,27 +10934,27 @@
       <c r="C50" s="29"/>
       <c r="E50" s="30">
         <f>(E15+E24+E32+E40+E48)*Допущения!$C$17</f>
-        <v>245700</v>
+        <v>245197.92449999999</v>
       </c>
       <c r="F50" s="30">
         <f>(F15+F24+F32+F40+F48)*Допущения!$C$17</f>
-        <v>513539.75999999995</v>
+        <v>485608.35846000002</v>
       </c>
       <c r="G50" s="30">
         <f>(G15+G24+G32+G40+G48)*Допущения!$C$17</f>
-        <v>1174236.7008</v>
+        <v>1084237.3471367999</v>
       </c>
       <c r="H50" s="30">
         <f>(H15+H24+H32+H40+H48)*Допущения!$C$17</f>
-        <v>2080446.3632639996</v>
+        <v>1912761.4613077436</v>
       </c>
       <c r="I50" s="30">
         <f>(I15+I24+I32+I40+I48)*Допущения!$C$17</f>
-        <v>3025182.3738931199</v>
+        <v>2776870.6797803636</v>
       </c>
       <c r="J50" s="22">
         <f t="shared" ref="J50:J51" si="10">SUM(E50:I50)</f>
-        <v>7039105.197957119</v>
+        <v>6504675.7711849064</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>154</v>
@@ -10976,27 +10967,27 @@
       <c r="C51" s="29"/>
       <c r="E51" s="27">
         <f t="shared" ref="E51:I51" si="11">E15+E24+E32+E40+E48+E50</f>
-        <v>1883700</v>
+        <v>1879850.7545</v>
       </c>
       <c r="F51" s="27">
         <f t="shared" si="11"/>
-        <v>3937138.1599999997</v>
+        <v>3722997.4148599999</v>
       </c>
       <c r="G51" s="27">
         <f t="shared" si="11"/>
-        <v>9002481.3728</v>
+        <v>8312486.3280488001</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="11"/>
-        <v>15950088.785023998</v>
+        <v>14664504.536692701</v>
       </c>
       <c r="I51" s="27">
         <f t="shared" si="11"/>
-        <v>23193064.866513919</v>
+        <v>21289341.878316123</v>
       </c>
       <c r="J51" s="27">
         <f t="shared" si="10"/>
-        <v>53966473.184337914</v>
+        <v>49869180.91241762</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11052,27 +11043,27 @@
       </c>
       <c r="E54" s="27">
         <f t="shared" ref="E54:I54" si="13">E51+E53</f>
-        <v>2514419.9999999306</v>
+        <v>2510570.7544999304</v>
       </c>
       <c r="F54" s="27">
         <f t="shared" si="13"/>
-        <v>4567858.1599999303</v>
+        <v>4353717.4148599301</v>
       </c>
       <c r="G54" s="27">
         <f t="shared" si="13"/>
-        <v>9633201.3727999311</v>
+        <v>8943206.3280487303</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="13"/>
-        <v>16580808.78502393</v>
+        <v>15295224.536692632</v>
       </c>
       <c r="I54" s="27">
         <f t="shared" si="13"/>
-        <v>23823784.866513848</v>
+        <v>21920061.878316052</v>
       </c>
       <c r="J54" s="27">
         <f t="shared" si="12"/>
-        <v>57120073.184337571</v>
+        <v>53022780.912417278</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11106,27 +11097,27 @@
       </c>
       <c r="E56" s="27">
         <f t="shared" ref="E56:I56" si="14">E54*E55</f>
-        <v>2514419.9999999306</v>
+        <v>2510570.7544999304</v>
       </c>
       <c r="F56" s="27">
         <f t="shared" si="14"/>
-        <v>3806548.4666666086</v>
+        <v>3628097.8457166087</v>
       </c>
       <c r="G56" s="27">
         <f t="shared" si="14"/>
-        <v>6689723.1755555077</v>
+        <v>6210559.9500338398</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="14"/>
-        <v>9595375.4542962555</v>
+        <v>8851403.0883637927</v>
       </c>
       <c r="I56" s="27">
         <f t="shared" si="14"/>
-        <v>11489093.78207651</v>
+        <v>10571017.495329887</v>
       </c>
       <c r="J56" s="27">
         <f>SUM(E56:I56)</f>
-        <v>34095160.878594808</v>
+        <v>31771649.133944057</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11149,11 +11140,11 @@
       <c r="B59" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="47">
         <f>J51</f>
-        <v>53966473.184337914</v>
-      </c>
-      <c r="F59" s="36"/>
+        <v>49869180.91241762</v>
+      </c>
+      <c r="F59" s="48"/>
       <c r="L59" s="12" t="s">
         <v>164</v>
       </c>
@@ -11162,11 +11153,11 @@
       <c r="B60" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="47">
         <f>J54</f>
-        <v>57120073.184337571</v>
-      </c>
-      <c r="F60" s="36"/>
+        <v>53022780.912417278</v>
+      </c>
+      <c r="F60" s="48"/>
       <c r="L60" s="12" t="s">
         <v>166</v>
       </c>
@@ -11175,11 +11166,11 @@
       <c r="B61" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="47">
         <f>J56</f>
-        <v>34095160.878594808</v>
-      </c>
-      <c r="F61" s="36"/>
+        <v>31771649.133944057</v>
+      </c>
+      <c r="F61" s="48"/>
       <c r="L61" s="12" t="s">
         <v>168</v>
       </c>
@@ -11188,11 +11179,11 @@
       <c r="B62" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="47">
         <f>J51/5</f>
-        <v>10793294.636867583</v>
-      </c>
-      <c r="F62" s="36"/>
+        <v>9973836.1824835241</v>
+      </c>
+      <c r="F62" s="48"/>
       <c r="L62" s="12" t="s">
         <v>170</v>
       </c>
@@ -11201,11 +11192,11 @@
       <c r="B63" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="48">
+      <c r="E63" s="47">
         <f>E15/12</f>
-        <v>15300</v>
-      </c>
-      <c r="F63" s="36"/>
+        <v>14429.402499999998</v>
+      </c>
+      <c r="F63" s="48"/>
       <c r="L63" s="12" t="s">
         <v>172</v>
       </c>
@@ -11218,7 +11209,7 @@
         <f>IF(E15/12&lt;=Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>ПРЕВЫШЕНИЕ бюджета</v>
       </c>
-      <c r="F64" s="36"/>
+      <c r="F64" s="48"/>
       <c r="L64" s="12" t="s">
         <v>174</v>
       </c>
@@ -11227,11 +11218,11 @@
       <c r="B65" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="35">
+      <c r="E65" s="50">
         <f>IFERROR(J51/SUM(Допущения!$C$8:$G$8),0)</f>
-        <v>1.4164428657306538</v>
-      </c>
-      <c r="F65" s="36"/>
+        <v>1.3089023861526934</v>
+      </c>
+      <c r="F65" s="48"/>
       <c r="L65" s="12" t="s">
         <v>176</v>
       </c>
@@ -11240,11 +11231,11 @@
       <c r="B66" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="35">
+      <c r="E66" s="50">
         <f>IFERROR(I51/Допущения!$G$7,0)</f>
-        <v>6.6265899618611197</v>
-      </c>
-      <c r="F66" s="36"/>
+        <v>6.0826691080903208</v>
+      </c>
+      <c r="F66" s="48"/>
       <c r="L66" s="12" t="s">
         <v>178</v>
       </c>
@@ -11253,11 +11244,11 @@
       <c r="B67" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="37">
+      <c r="E67" s="51">
         <f>IFERROR(J51/SUM(Допущения!$C$10:$G$10),0)</f>
-        <v>5.0234080968386774E-2</v>
-      </c>
-      <c r="F67" s="36"/>
+        <v>4.6420162815244921E-2</v>
+      </c>
+      <c r="F67" s="48"/>
       <c r="L67" s="12" t="s">
         <v>180</v>
       </c>
@@ -11266,11 +11257,11 @@
       <c r="B68" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="38">
+      <c r="E68" s="52">
         <f>IFERROR(J15/J51,0)</f>
-        <v>0.18711617424965674</v>
-      </c>
-      <c r="F68" s="36"/>
+        <v>0.17997947908845238</v>
+      </c>
+      <c r="F68" s="48"/>
       <c r="L68" s="12" t="s">
         <v>182</v>
       </c>
@@ -11279,11 +11270,11 @@
       <c r="B69" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="38">
+      <c r="E69" s="52">
         <f>IFERROR(J32/J51,0)</f>
-        <v>0.51815503867529722</v>
-      </c>
-      <c r="F69" s="36"/>
+        <v>0.53551912245966182</v>
+      </c>
+      <c r="F69" s="48"/>
       <c r="L69" s="12" t="s">
         <v>184</v>
       </c>
@@ -11292,71 +11283,71 @@
       <c r="B70" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="38">
+      <c r="E70" s="52">
         <f>IFERROR(J40/J51,0)</f>
-        <v>0.10312132624177295</v>
-      </c>
-      <c r="F70" s="36"/>
+        <v>0.11159385788055466</v>
+      </c>
+      <c r="F70" s="48"/>
       <c r="L70" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="39" t="s">
+      <c r="B72" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="36"/>
+      <c r="L72" s="36"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="40" t="s">
+      <c r="B73" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="41"/>
-      <c r="D73" s="41"/>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
-      <c r="L73" s="42"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40"/>
+      <c r="I73" s="40"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
+      <c r="L73" s="41"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="43"/>
-      <c r="C74" s="33"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="33"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="33"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="33"/>
-      <c r="L74" s="44"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="43"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="45"/>
-      <c r="C75" s="46"/>
-      <c r="D75" s="46"/>
-      <c r="E75" s="46"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
-      <c r="H75" s="46"/>
-      <c r="I75" s="46"/>
-      <c r="J75" s="46"/>
-      <c r="K75" s="46"/>
-      <c r="L75" s="47"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="45"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="45"/>
+      <c r="L75" s="46"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/sprint-9/Task2/tco-model.xlsx
+++ b/sprint-9/Task2/tco-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ya.practicum\solution-architect\ya.solution-architecture-tasks\sprint-9\Task2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031ABB52-0289-4D61-9832-BA4BAD31B74E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2E9846-5A84-40A5-BB4C-CF232328D3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1725" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" r:id="rId1"/>
@@ -944,14 +944,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -968,6 +962,12 @@
     <xf numFmtId="164" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1377,7 +1377,7 @@
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="51" t="s">
         <v>51</v>
       </c>
       <c r="C28" s="36"/>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="31" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="52" t="s">
         <v>99</v>
       </c>
       <c r="C32" s="36"/>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="K15" s="28">
         <f>IFERROR(J15/$J$51,0)</f>
-        <v>7.9834206777594133E-2</v>
+        <v>7.9767305523476259E-2</v>
       </c>
       <c r="L15" s="26"/>
     </row>
@@ -4348,31 +4348,31 @@
         <v>64</v>
       </c>
       <c r="D20" s="17">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E20" s="22">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F20" s="22">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="22">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H20" s="22">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>8333.3333333333339</v>
       </c>
       <c r="I20" s="22">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>11666.666666666666</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>27500</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="24" t="s">
@@ -4502,31 +4502,31 @@
       <c r="D24" s="26"/>
       <c r="E24" s="27">
         <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" si="3"/>
-        <v>6096</v>
+        <v>8096</v>
       </c>
       <c r="G24" s="27">
         <f t="shared" si="3"/>
-        <v>13399.68</v>
+        <v>18399.68</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="3"/>
-        <v>21511.654399999999</v>
+        <v>29844.987733333335</v>
       </c>
       <c r="I24" s="27">
         <f t="shared" si="3"/>
-        <v>29632.586752000003</v>
+        <v>41299.253418666667</v>
       </c>
       <c r="J24" s="27">
         <f t="shared" si="3"/>
-        <v>73039.921151999995</v>
+        <v>100539.921152</v>
       </c>
       <c r="K24" s="28">
         <f>IFERROR(J24/$J$51,0)</f>
-        <v>1.9370422718573538E-3</v>
+        <v>2.6641167348779638E-3</v>
       </c>
       <c r="L24" s="26"/>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="K32" s="28">
         <f>IFERROR(J32/$J$51,0)</f>
-        <v>0.70824908340661341</v>
+        <v>0.70765556899944027</v>
       </c>
       <c r="L32" s="26"/>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="K40" s="28">
         <f>IFERROR(J40/$J$51,0)</f>
-        <v>6.6717906328484761E-2</v>
+        <v>6.6661996565168274E-2</v>
       </c>
       <c r="L40" s="26"/>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="K48" s="28">
         <f>IFERROR(J48/$J$51,0)</f>
-        <v>1.2826978606754847E-2</v>
+        <v>1.2816229568341704E-2</v>
       </c>
       <c r="L48" s="26"/>
     </row>
@@ -5282,27 +5282,27 @@
       <c r="C50" s="29"/>
       <c r="E50" s="30">
         <f>(E15+E24+E32+E40+E48)*Допущения!$C$17</f>
-        <v>112619.3985</v>
+        <v>112694.3985</v>
       </c>
       <c r="F50" s="30">
         <f>(F15+F24+F32+F40+F48)*Допущения!$C$17</f>
-        <v>294125.05446000001</v>
+        <v>294425.05446000001</v>
       </c>
       <c r="G50" s="30">
         <f>(G15+G24+G32+G40+G48)*Допущения!$C$17</f>
-        <v>784386.95113679999</v>
+        <v>785136.95113679999</v>
       </c>
       <c r="H50" s="30">
         <f>(H15+H24+H32+H40+H48)*Допущения!$C$17</f>
-        <v>1492484.3424277438</v>
+        <v>1493734.3424277438</v>
       </c>
       <c r="I50" s="30">
         <f>(I15+I24+I32+I40+I48)*Допущения!$C$17</f>
-        <v>2234679.7267499636</v>
+        <v>2236429.7267499631</v>
       </c>
       <c r="J50" s="22">
         <f t="shared" ref="J50:J51" si="10">SUM(E50:I50)</f>
-        <v>4918295.4732745066</v>
+        <v>4922420.4732745066</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>154</v>
@@ -5315,27 +5315,27 @@
       <c r="C51" s="29"/>
       <c r="E51" s="27">
         <f t="shared" ref="E51:I51" si="11">E15+E24+E32+E40+E48+E50</f>
-        <v>863415.3885</v>
+        <v>863990.3885</v>
       </c>
       <c r="F51" s="27">
         <f t="shared" si="11"/>
-        <v>2254958.75086</v>
+        <v>2257258.75086</v>
       </c>
       <c r="G51" s="27">
         <f t="shared" si="11"/>
-        <v>6013633.2920488007</v>
+        <v>6019383.2920488007</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="11"/>
-        <v>11442379.958612703</v>
+        <v>11451963.291946037</v>
       </c>
       <c r="I51" s="27">
         <f t="shared" si="11"/>
-        <v>17132544.571749721</v>
+        <v>17145961.238416385</v>
       </c>
       <c r="J51" s="27">
         <f t="shared" si="10"/>
-        <v>37706931.96177122</v>
+        <v>37738556.96177122</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5391,27 +5391,27 @@
       </c>
       <c r="E54" s="27">
         <f t="shared" ref="E54:I54" si="13">E51+E53</f>
-        <v>1494135.3884999305</v>
+        <v>1494710.3884999305</v>
       </c>
       <c r="F54" s="27">
         <f t="shared" si="13"/>
-        <v>2885678.7508599306</v>
+        <v>2887978.7508599306</v>
       </c>
       <c r="G54" s="27">
         <f t="shared" si="13"/>
-        <v>6644353.2920487309</v>
+        <v>6650103.2920487309</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="13"/>
-        <v>12073099.958612634</v>
+        <v>12082683.291945968</v>
       </c>
       <c r="I54" s="27">
         <f t="shared" si="13"/>
-        <v>17763264.57174965</v>
+        <v>17776681.238416314</v>
       </c>
       <c r="J54" s="27">
         <f t="shared" si="12"/>
-        <v>40860531.961770877</v>
+        <v>40892156.961770877</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5445,27 +5445,27 @@
       </c>
       <c r="E56" s="27">
         <f t="shared" ref="E56:I56" si="14">E54*E55</f>
-        <v>1494135.3884999305</v>
+        <v>1494710.3884999305</v>
       </c>
       <c r="F56" s="27">
         <f t="shared" si="14"/>
-        <v>2404732.2923832755</v>
+        <v>2406648.9590499424</v>
       </c>
       <c r="G56" s="27">
         <f t="shared" si="14"/>
-        <v>4614134.2305893963</v>
+        <v>4618127.2861449523</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="14"/>
-        <v>6986747.6612341637</v>
+        <v>6992293.5717279911</v>
       </c>
       <c r="I56" s="27">
         <f t="shared" si="14"/>
-        <v>8566389.1646169219</v>
+        <v>8572859.3935263865</v>
       </c>
       <c r="J56" s="27">
         <f>SUM(E56:I56)</f>
-        <v>24066138.737323686</v>
+        <v>24084639.598949201</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5488,11 +5488,11 @@
       <c r="B59" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="47">
+      <c r="E59" s="45">
         <f>J51</f>
-        <v>37706931.96177122</v>
-      </c>
-      <c r="F59" s="48"/>
+        <v>37738556.96177122</v>
+      </c>
+      <c r="F59" s="46"/>
       <c r="L59" s="12" t="s">
         <v>164</v>
       </c>
@@ -5501,11 +5501,11 @@
       <c r="B60" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="47">
+      <c r="E60" s="45">
         <f>J54</f>
-        <v>40860531.961770877</v>
-      </c>
-      <c r="F60" s="48"/>
+        <v>40892156.961770877</v>
+      </c>
+      <c r="F60" s="46"/>
       <c r="L60" s="12" t="s">
         <v>166</v>
       </c>
@@ -5514,11 +5514,11 @@
       <c r="B61" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="47">
+      <c r="E61" s="45">
         <f>J56</f>
-        <v>24066138.737323686</v>
-      </c>
-      <c r="F61" s="48"/>
+        <v>24084639.598949201</v>
+      </c>
+      <c r="F61" s="46"/>
       <c r="L61" s="12" t="s">
         <v>168</v>
       </c>
@@ -5527,11 +5527,11 @@
       <c r="B62" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="47">
+      <c r="E62" s="45">
         <f>J51/5</f>
-        <v>7541386.3923542444</v>
-      </c>
-      <c r="F62" s="48"/>
+        <v>7547711.3923542444</v>
+      </c>
+      <c r="F62" s="46"/>
       <c r="L62" s="12" t="s">
         <v>170</v>
       </c>
@@ -5540,11 +5540,11 @@
       <c r="B63" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="47">
+      <c r="E63" s="45">
         <f>E15/12</f>
         <v>5391.3325000000004</v>
       </c>
-      <c r="F63" s="48"/>
+      <c r="F63" s="46"/>
       <c r="L63" s="12" t="s">
         <v>172</v>
       </c>
@@ -5553,11 +5553,11 @@
       <c r="B64" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="49" t="str">
+      <c r="E64" s="47" t="str">
         <f>IF(E15/12&lt;=Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>В бюджете CFO</v>
       </c>
-      <c r="F64" s="48"/>
+      <c r="F64" s="46"/>
       <c r="L64" s="12" t="s">
         <v>174</v>
       </c>
@@ -5566,11 +5566,11 @@
       <c r="B65" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="50">
+      <c r="E65" s="48">
         <f>IFERROR(J51/SUM(Допущения!$C$8:$G$8),0)</f>
-        <v>0.98968325358979581</v>
-      </c>
-      <c r="F65" s="48"/>
+        <v>0.99051330608323407</v>
+      </c>
+      <c r="F65" s="46"/>
       <c r="L65" s="12" t="s">
         <v>176</v>
       </c>
@@ -5579,11 +5579,11 @@
       <c r="B66" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="50">
+      <c r="E66" s="48">
         <f>IFERROR(I51/Допущения!$G$7,0)</f>
-        <v>4.8950127347856345</v>
-      </c>
-      <c r="F66" s="48"/>
+        <v>4.8988460681189672</v>
+      </c>
+      <c r="F66" s="46"/>
       <c r="L66" s="12" t="s">
         <v>178</v>
       </c>
@@ -5592,11 +5592,11 @@
       <c r="B67" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="51">
+      <c r="E67" s="49">
         <f>IFERROR(J51/SUM(Допущения!$C$10:$G$10),0)</f>
-        <v>3.5099070987406888E-2</v>
-      </c>
-      <c r="F67" s="48"/>
+        <v>3.5128508760840754E-2</v>
+      </c>
+      <c r="F67" s="46"/>
       <c r="L67" s="12" t="s">
         <v>180</v>
       </c>
@@ -5605,11 +5605,11 @@
       <c r="B68" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="52">
+      <c r="E68" s="50">
         <f>IFERROR(J15/J51,0)</f>
-        <v>7.9834206777594133E-2</v>
-      </c>
-      <c r="F68" s="48"/>
+        <v>7.9767305523476259E-2</v>
+      </c>
+      <c r="F68" s="46"/>
       <c r="L68" s="12" t="s">
         <v>182</v>
       </c>
@@ -5618,11 +5618,11 @@
       <c r="B69" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="52">
+      <c r="E69" s="50">
         <f>IFERROR(J32/J51,0)</f>
-        <v>0.70824908340661341</v>
-      </c>
-      <c r="F69" s="48"/>
+        <v>0.70765556899944027</v>
+      </c>
+      <c r="F69" s="46"/>
       <c r="L69" s="12" t="s">
         <v>184</v>
       </c>
@@ -5631,18 +5631,18 @@
       <c r="B70" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="52">
+      <c r="E70" s="50">
         <f>IFERROR(J40/J51,0)</f>
-        <v>6.6717906328484761E-2</v>
-      </c>
-      <c r="F70" s="48"/>
+        <v>6.6661996565168274E-2</v>
+      </c>
+      <c r="F70" s="46"/>
       <c r="L70" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="38" t="s">
+      <c r="B72" s="35" t="s">
         <v>187</v>
       </c>
       <c r="C72" s="36"/>
@@ -5657,22 +5657,22 @@
       <c r="L72" s="36"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="39" t="s">
+      <c r="B73" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40"/>
-      <c r="K73" s="40"/>
-      <c r="L73" s="41"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="39"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="42"/>
+      <c r="B74" s="40"/>
       <c r="C74" s="36"/>
       <c r="D74" s="36"/>
       <c r="E74" s="36"/>
@@ -5682,20 +5682,20 @@
       <c r="I74" s="36"/>
       <c r="J74" s="36"/>
       <c r="K74" s="36"/>
-      <c r="L74" s="43"/>
+      <c r="L74" s="41"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="44"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45"/>
-      <c r="I75" s="45"/>
-      <c r="J75" s="45"/>
-      <c r="K75" s="45"/>
-      <c r="L75" s="46"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="43"/>
+      <c r="E75" s="43"/>
+      <c r="F75" s="43"/>
+      <c r="G75" s="43"/>
+      <c r="H75" s="43"/>
+      <c r="I75" s="43"/>
+      <c r="J75" s="43"/>
+      <c r="K75" s="43"/>
+      <c r="L75" s="44"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="K15" s="28">
         <f>IFERROR(J15/$J$51,0)</f>
-        <v>9.102274974229374E-2</v>
+        <v>9.0949848779131981E-2</v>
       </c>
       <c r="L15" s="26"/>
     </row>
@@ -7174,31 +7174,31 @@
         <v>64</v>
       </c>
       <c r="D20" s="17">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E20" s="22">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F20" s="22">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="22">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H20" s="22">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>8333.3333333333339</v>
       </c>
       <c r="I20" s="22">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>11666.666666666666</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>27500</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="24" t="s">
@@ -7328,31 +7328,31 @@
       <c r="D24" s="26"/>
       <c r="E24" s="27">
         <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
-        <v>3600</v>
+        <v>4100</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" si="3"/>
-        <v>9144</v>
+        <v>11144</v>
       </c>
       <c r="G24" s="27">
         <f t="shared" si="3"/>
-        <v>20099.52</v>
+        <v>25099.52</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="3"/>
-        <v>32267.481600000003</v>
+        <v>40600.814933333335</v>
       </c>
       <c r="I24" s="27">
         <f t="shared" si="3"/>
-        <v>44448.880128000004</v>
+        <v>56115.546794666669</v>
       </c>
       <c r="J24" s="27">
         <f t="shared" si="3"/>
-        <v>109559.88172799999</v>
+        <v>137059.88172800001</v>
       </c>
       <c r="K24" s="28">
         <f>IFERROR(J24/$J$51,0)</f>
-        <v>2.7768492636581219E-3</v>
+        <v>3.471068094366011E-3</v>
       </c>
       <c r="L24" s="26"/>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="K32" s="28">
         <f>IFERROR(J32/$J$51,0)</f>
-        <v>0.67687421326756469</v>
+        <v>0.67633209844213626</v>
       </c>
       <c r="L32" s="26"/>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="K40" s="28">
         <f>IFERROR(J40/$J$51,0)</f>
-        <v>8.3084282362526865E-2</v>
+        <v>8.3017739391401738E-2</v>
       </c>
       <c r="L40" s="26"/>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K48" s="28">
         <f>IFERROR(J48/$J$51,0)</f>
-        <v>1.5807122755260878E-2</v>
+        <v>1.5794462684268328E-2</v>
       </c>
       <c r="L48" s="26"/>
     </row>
@@ -8108,27 +8108,27 @@
       <c r="C50" s="29"/>
       <c r="E50" s="30">
         <f>(E15+E24+E32+E40+E48)*Допущения!$C$17</f>
-        <v>135089.39849999998</v>
+        <v>135164.39849999998</v>
       </c>
       <c r="F50" s="30">
         <f>(F15+F24+F32+F40+F48)*Допущения!$C$17</f>
-        <v>324187.19399999996</v>
+        <v>324487.19399999996</v>
       </c>
       <c r="G50" s="30">
         <f>(G15+G24+G32+G40+G48)*Допущения!$C$17</f>
-        <v>827849.07299999997</v>
+        <v>828599.07299999997</v>
       </c>
       <c r="H50" s="30">
         <f>(H15+H24+H32+H40+H48)*Допущения!$C$17</f>
-        <v>1550861.0924399996</v>
+        <v>1552111.09244</v>
       </c>
       <c r="I50" s="30">
         <f>(I15+I24+I32+I40+I48)*Допущения!$C$17</f>
-        <v>2308284.4289231999</v>
+        <v>2310034.4289231999</v>
       </c>
       <c r="J50" s="22">
         <f t="shared" ref="J50:J51" si="10">SUM(E50:I50)</f>
-        <v>5146271.1868631989</v>
+        <v>5150396.1868631998</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>154</v>
@@ -8141,27 +8141,27 @@
       <c r="C51" s="29"/>
       <c r="E51" s="27">
         <f t="shared" ref="E51:I51" si="11">E15+E24+E32+E40+E48+E50</f>
-        <v>1035685.3885</v>
+        <v>1036260.3885</v>
       </c>
       <c r="F51" s="27">
         <f t="shared" si="11"/>
-        <v>2485435.1540000001</v>
+        <v>2487735.1540000001</v>
       </c>
       <c r="G51" s="27">
         <f t="shared" si="11"/>
-        <v>6346842.8930000002</v>
+        <v>6352592.8930000002</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="11"/>
-        <v>11889935.042039998</v>
+        <v>11899518.375373334</v>
       </c>
       <c r="I51" s="27">
         <f t="shared" si="11"/>
-        <v>17696847.2884112</v>
+        <v>17710263.955077864</v>
       </c>
       <c r="J51" s="27">
         <f t="shared" si="10"/>
-        <v>39454745.765951201</v>
+        <v>39486370.765951201</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8217,27 +8217,27 @@
       </c>
       <c r="E54" s="27">
         <f t="shared" ref="E54:I54" si="13">E51+E53</f>
-        <v>1666405.3884999305</v>
+        <v>1666980.3884999305</v>
       </c>
       <c r="F54" s="27">
         <f t="shared" si="13"/>
-        <v>3116155.1539999307</v>
+        <v>3118455.1539999307</v>
       </c>
       <c r="G54" s="27">
         <f t="shared" si="13"/>
-        <v>6977562.8929999303</v>
+        <v>6983312.8929999303</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="13"/>
-        <v>12520655.042039929</v>
+        <v>12530238.375373265</v>
       </c>
       <c r="I54" s="27">
         <f t="shared" si="13"/>
-        <v>18327567.288411129</v>
+        <v>18340983.955077793</v>
       </c>
       <c r="J54" s="27">
         <f t="shared" si="12"/>
-        <v>42608345.765950844</v>
+        <v>42639970.765950844</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8271,27 +8271,27 @@
       </c>
       <c r="E56" s="27">
         <f t="shared" ref="E56:I56" si="14">E54*E55</f>
-        <v>1666405.3884999305</v>
+        <v>1666980.3884999305</v>
       </c>
       <c r="F56" s="27">
         <f t="shared" si="14"/>
-        <v>2596795.9616666092</v>
+        <v>2598712.6283332757</v>
       </c>
       <c r="G56" s="27">
         <f t="shared" si="14"/>
-        <v>4845529.7868055068</v>
+        <v>4849522.8423610628</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="14"/>
-        <v>7245749.4456249587</v>
+        <v>7251295.356118788</v>
       </c>
       <c r="I56" s="27">
         <f t="shared" si="14"/>
-        <v>8838525.8914019726</v>
+        <v>8844996.1203114372</v>
       </c>
       <c r="J56" s="27">
         <f>SUM(E56:I56)</f>
-        <v>25193006.473998979</v>
+        <v>25211507.335624494</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8314,11 +8314,11 @@
       <c r="B59" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="47">
+      <c r="E59" s="45">
         <f>J51</f>
-        <v>39454745.765951201</v>
-      </c>
-      <c r="F59" s="48"/>
+        <v>39486370.765951201</v>
+      </c>
+      <c r="F59" s="46"/>
       <c r="L59" s="12" t="s">
         <v>164</v>
       </c>
@@ -8327,11 +8327,11 @@
       <c r="B60" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="47">
+      <c r="E60" s="45">
         <f>J54</f>
-        <v>42608345.765950844</v>
-      </c>
-      <c r="F60" s="48"/>
+        <v>42639970.765950844</v>
+      </c>
+      <c r="F60" s="46"/>
       <c r="L60" s="12" t="s">
         <v>166</v>
       </c>
@@ -8340,11 +8340,11 @@
       <c r="B61" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="47">
+      <c r="E61" s="45">
         <f>J56</f>
-        <v>25193006.473998979</v>
-      </c>
-      <c r="F61" s="48"/>
+        <v>25211507.335624494</v>
+      </c>
+      <c r="F61" s="46"/>
       <c r="L61" s="12" t="s">
         <v>168</v>
       </c>
@@ -8353,11 +8353,11 @@
       <c r="B62" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="47">
+      <c r="E62" s="45">
         <f>J51/5</f>
-        <v>7890949.1531902403</v>
-      </c>
-      <c r="F62" s="48"/>
+        <v>7897274.1531902403</v>
+      </c>
+      <c r="F62" s="46"/>
       <c r="L62" s="12" t="s">
         <v>170</v>
       </c>
@@ -8366,11 +8366,11 @@
       <c r="B63" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="47">
+      <c r="E63" s="45">
         <f>E15/12</f>
         <v>5441.3325000000004</v>
       </c>
-      <c r="F63" s="48"/>
+      <c r="F63" s="46"/>
       <c r="L63" s="12" t="s">
         <v>172</v>
       </c>
@@ -8379,11 +8379,11 @@
       <c r="B64" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="49" t="str">
+      <c r="E64" s="47" t="str">
         <f>IF(E15/12&lt;=Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>В бюджете CFO</v>
       </c>
-      <c r="F64" s="48"/>
+      <c r="F64" s="46"/>
       <c r="L64" s="12" t="s">
         <v>174</v>
       </c>
@@ -8392,11 +8392,11 @@
       <c r="B65" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="50">
+      <c r="E65" s="48">
         <f>IFERROR(J51/SUM(Допущения!$C$8:$G$8),0)</f>
-        <v>1.0355576316522626</v>
-      </c>
-      <c r="F65" s="48"/>
+        <v>1.0363876841457009</v>
+      </c>
+      <c r="F65" s="46"/>
       <c r="L65" s="12" t="s">
         <v>176</v>
       </c>
@@ -8405,11 +8405,11 @@
       <c r="B66" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="50">
+      <c r="E66" s="48">
         <f>IFERROR(I51/Допущения!$G$7,0)</f>
-        <v>5.0562420824031999</v>
-      </c>
-      <c r="F66" s="48"/>
+        <v>5.0600754157365326</v>
+      </c>
+      <c r="F66" s="46"/>
       <c r="L66" s="12" t="s">
         <v>178</v>
       </c>
@@ -8418,11 +8418,11 @@
       <c r="B67" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="51">
+      <c r="E67" s="49">
         <f>IFERROR(J51/SUM(Допущения!$C$10:$G$10),0)</f>
-        <v>3.6726003691660805E-2</v>
-      </c>
-      <c r="F67" s="48"/>
+        <v>3.6755441465094671E-2</v>
+      </c>
+      <c r="F67" s="46"/>
       <c r="L67" s="12" t="s">
         <v>180</v>
       </c>
@@ -8431,11 +8431,11 @@
       <c r="B68" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="52">
+      <c r="E68" s="50">
         <f>IFERROR(J15/J51,0)</f>
-        <v>9.102274974229374E-2</v>
-      </c>
-      <c r="F68" s="48"/>
+        <v>9.0949848779131981E-2</v>
+      </c>
+      <c r="F68" s="46"/>
       <c r="L68" s="12" t="s">
         <v>182</v>
       </c>
@@ -8444,11 +8444,11 @@
       <c r="B69" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="52">
+      <c r="E69" s="50">
         <f>IFERROR(J32/J51,0)</f>
-        <v>0.67687421326756469</v>
-      </c>
-      <c r="F69" s="48"/>
+        <v>0.67633209844213626</v>
+      </c>
+      <c r="F69" s="46"/>
       <c r="L69" s="12" t="s">
         <v>184</v>
       </c>
@@ -8457,18 +8457,18 @@
       <c r="B70" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="52">
+      <c r="E70" s="50">
         <f>IFERROR(J40/J51,0)</f>
-        <v>8.3084282362526865E-2</v>
-      </c>
-      <c r="F70" s="48"/>
+        <v>8.3017739391401738E-2</v>
+      </c>
+      <c r="F70" s="46"/>
       <c r="L70" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="38" t="s">
+      <c r="B72" s="35" t="s">
         <v>187</v>
       </c>
       <c r="C72" s="36"/>
@@ -8483,22 +8483,22 @@
       <c r="L72" s="36"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="39" t="s">
+      <c r="B73" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40"/>
-      <c r="K73" s="40"/>
-      <c r="L73" s="41"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="39"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="42"/>
+      <c r="B74" s="40"/>
       <c r="C74" s="36"/>
       <c r="D74" s="36"/>
       <c r="E74" s="36"/>
@@ -8508,20 +8508,20 @@
       <c r="I74" s="36"/>
       <c r="J74" s="36"/>
       <c r="K74" s="36"/>
-      <c r="L74" s="43"/>
+      <c r="L74" s="41"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="44"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45"/>
-      <c r="I75" s="45"/>
-      <c r="J75" s="45"/>
-      <c r="K75" s="45"/>
-      <c r="L75" s="46"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="43"/>
+      <c r="E75" s="43"/>
+      <c r="F75" s="43"/>
+      <c r="G75" s="43"/>
+      <c r="H75" s="43"/>
+      <c r="I75" s="43"/>
+      <c r="J75" s="43"/>
+      <c r="K75" s="43"/>
+      <c r="L75" s="44"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="K15" s="28">
         <f>IFERROR(J15/$J$51,0)</f>
-        <v>0.17997947908845238</v>
+        <v>0.17986541577981241</v>
       </c>
       <c r="L15" s="26"/>
     </row>
@@ -10000,31 +10000,31 @@
         <v>64</v>
       </c>
       <c r="D20" s="17">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E20" s="22">
         <f t="array" ref="E20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),1))</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F20" s="22">
         <f t="array" ref="F20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),2))</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G20" s="22">
         <f t="array" ref="G20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),3))</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H20" s="22">
         <f t="array" ref="H20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),4))</f>
-        <v>0</v>
+        <v>8333.3333333333339</v>
       </c>
       <c r="I20" s="22">
         <f t="array" ref="I20">IF($D20="","",$D20*INDEX(Допущения!$C$25:$G$30,MATCH($C20,Допущения!$B$25:$B$30,0),5))</f>
-        <v>0</v>
+        <v>11666.666666666666</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>27500</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="24" t="s">
@@ -10154,31 +10154,31 @@
       <c r="D24" s="26"/>
       <c r="E24" s="27">
         <f t="shared" ref="E24:J24" si="3">SUM(E18:E23)</f>
-        <v>167800</v>
+        <v>168300</v>
       </c>
       <c r="F24" s="27">
         <f t="shared" si="3"/>
-        <v>181224</v>
+        <v>183224</v>
       </c>
       <c r="G24" s="27">
         <f t="shared" si="3"/>
-        <v>195721.92</v>
+        <v>200721.92000000001</v>
       </c>
       <c r="H24" s="27">
         <f t="shared" si="3"/>
-        <v>211379.67360000004</v>
+        <v>219713.00693333338</v>
       </c>
       <c r="I24" s="27">
         <f t="shared" si="3"/>
-        <v>228290.04748800004</v>
+        <v>239956.71415466673</v>
       </c>
       <c r="J24" s="27">
         <f t="shared" si="3"/>
-        <v>984415.64108800015</v>
+        <v>1011915.6410880001</v>
       </c>
       <c r="K24" s="28">
         <f>IFERROR(J24/$J$51,0)</f>
-        <v>1.9739960093125911E-2</v>
+        <v>2.0278543053273392E-2</v>
       </c>
       <c r="L24" s="26"/>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="K32" s="28">
         <f>IFERROR(J32/$J$51,0)</f>
-        <v>0.53551912245966182</v>
+        <v>0.53517973330675894</v>
       </c>
       <c r="L32" s="26"/>
     </row>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="K40" s="28">
         <f>IFERROR(J40/$J$51,0)</f>
-        <v>0.11159385788055466</v>
+        <v>0.11152313445853887</v>
       </c>
       <c r="L40" s="26"/>
     </row>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="K48" s="28">
         <f>IFERROR(J48/$J$51,0)</f>
-        <v>2.2732797869509679E-2</v>
+        <v>2.2718390792920873E-2</v>
       </c>
       <c r="L48" s="26"/>
     </row>
@@ -10934,27 +10934,27 @@
       <c r="C50" s="29"/>
       <c r="E50" s="30">
         <f>(E15+E24+E32+E40+E48)*Допущения!$C$17</f>
-        <v>245197.92449999999</v>
+        <v>245272.92449999999</v>
       </c>
       <c r="F50" s="30">
         <f>(F15+F24+F32+F40+F48)*Допущения!$C$17</f>
-        <v>485608.35846000002</v>
+        <v>485908.35846000002</v>
       </c>
       <c r="G50" s="30">
         <f>(G15+G24+G32+G40+G48)*Допущения!$C$17</f>
-        <v>1084237.3471367999</v>
+        <v>1084987.3471367999</v>
       </c>
       <c r="H50" s="30">
         <f>(H15+H24+H32+H40+H48)*Допущения!$C$17</f>
-        <v>1912761.4613077436</v>
+        <v>1914011.461307744</v>
       </c>
       <c r="I50" s="30">
         <f>(I15+I24+I32+I40+I48)*Допущения!$C$17</f>
-        <v>2776870.6797803636</v>
+        <v>2778620.6797803636</v>
       </c>
       <c r="J50" s="22">
         <f t="shared" ref="J50:J51" si="10">SUM(E50:I50)</f>
-        <v>6504675.7711849064</v>
+        <v>6508800.7711849082</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>154</v>
@@ -10967,27 +10967,27 @@
       <c r="C51" s="29"/>
       <c r="E51" s="27">
         <f t="shared" ref="E51:I51" si="11">E15+E24+E32+E40+E48+E50</f>
-        <v>1879850.7545</v>
+        <v>1880425.7545</v>
       </c>
       <c r="F51" s="27">
         <f t="shared" si="11"/>
-        <v>3722997.4148599999</v>
+        <v>3725297.4148599999</v>
       </c>
       <c r="G51" s="27">
         <f t="shared" si="11"/>
-        <v>8312486.3280488001</v>
+        <v>8318236.3280488001</v>
       </c>
       <c r="H51" s="27">
         <f t="shared" si="11"/>
-        <v>14664504.536692701</v>
+        <v>14674087.870026037</v>
       </c>
       <c r="I51" s="27">
         <f t="shared" si="11"/>
-        <v>21289341.878316123</v>
+        <v>21302758.544982787</v>
       </c>
       <c r="J51" s="27">
         <f t="shared" si="10"/>
-        <v>49869180.91241762</v>
+        <v>49900805.91241762</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11043,27 +11043,27 @@
       </c>
       <c r="E54" s="27">
         <f t="shared" ref="E54:I54" si="13">E51+E53</f>
-        <v>2510570.7544999304</v>
+        <v>2511145.7544999304</v>
       </c>
       <c r="F54" s="27">
         <f t="shared" si="13"/>
-        <v>4353717.4148599301</v>
+        <v>4356017.4148599301</v>
       </c>
       <c r="G54" s="27">
         <f t="shared" si="13"/>
-        <v>8943206.3280487303</v>
+        <v>8948956.3280487303</v>
       </c>
       <c r="H54" s="27">
         <f t="shared" si="13"/>
-        <v>15295224.536692632</v>
+        <v>15304807.870025968</v>
       </c>
       <c r="I54" s="27">
         <f t="shared" si="13"/>
-        <v>21920061.878316052</v>
+        <v>21933478.544982716</v>
       </c>
       <c r="J54" s="27">
         <f t="shared" si="12"/>
-        <v>53022780.912417278</v>
+        <v>53054405.912417278</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11097,27 +11097,27 @@
       </c>
       <c r="E56" s="27">
         <f t="shared" ref="E56:I56" si="14">E54*E55</f>
-        <v>2510570.7544999304</v>
+        <v>2511145.7544999304</v>
       </c>
       <c r="F56" s="27">
         <f t="shared" si="14"/>
-        <v>3628097.8457166087</v>
+        <v>3630014.5123832752</v>
       </c>
       <c r="G56" s="27">
         <f t="shared" si="14"/>
-        <v>6210559.9500338398</v>
+        <v>6214553.0055893958</v>
       </c>
       <c r="H56" s="27">
         <f t="shared" si="14"/>
-        <v>8851403.0883637927</v>
+        <v>8856948.9988576211</v>
       </c>
       <c r="I56" s="27">
         <f t="shared" si="14"/>
-        <v>10571017.495329887</v>
+        <v>10577487.724239351</v>
       </c>
       <c r="J56" s="27">
         <f>SUM(E56:I56)</f>
-        <v>31771649.133944057</v>
+        <v>31790149.995569572</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11140,11 +11140,11 @@
       <c r="B59" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E59" s="47">
+      <c r="E59" s="45">
         <f>J51</f>
-        <v>49869180.91241762</v>
-      </c>
-      <c r="F59" s="48"/>
+        <v>49900805.91241762</v>
+      </c>
+      <c r="F59" s="46"/>
       <c r="L59" s="12" t="s">
         <v>164</v>
       </c>
@@ -11153,11 +11153,11 @@
       <c r="B60" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E60" s="47">
+      <c r="E60" s="45">
         <f>J54</f>
-        <v>53022780.912417278</v>
-      </c>
-      <c r="F60" s="48"/>
+        <v>53054405.912417278</v>
+      </c>
+      <c r="F60" s="46"/>
       <c r="L60" s="12" t="s">
         <v>166</v>
       </c>
@@ -11166,11 +11166,11 @@
       <c r="B61" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="E61" s="47">
+      <c r="E61" s="45">
         <f>J56</f>
-        <v>31771649.133944057</v>
-      </c>
-      <c r="F61" s="48"/>
+        <v>31790149.995569572</v>
+      </c>
+      <c r="F61" s="46"/>
       <c r="L61" s="12" t="s">
         <v>168</v>
       </c>
@@ -11179,11 +11179,11 @@
       <c r="B62" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="47">
+      <c r="E62" s="45">
         <f>J51/5</f>
-        <v>9973836.1824835241</v>
-      </c>
-      <c r="F62" s="48"/>
+        <v>9980161.1824835241</v>
+      </c>
+      <c r="F62" s="46"/>
       <c r="L62" s="12" t="s">
         <v>170</v>
       </c>
@@ -11192,11 +11192,11 @@
       <c r="B63" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="47">
+      <c r="E63" s="45">
         <f>E15/12</f>
         <v>14429.402499999998</v>
       </c>
-      <c r="F63" s="48"/>
+      <c r="F63" s="46"/>
       <c r="L63" s="12" t="s">
         <v>172</v>
       </c>
@@ -11205,11 +11205,11 @@
       <c r="B64" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="49" t="str">
+      <c r="E64" s="47" t="str">
         <f>IF(E15/12&lt;=Допущения!$C$18,"В бюджете CFO","ПРЕВЫШЕНИЕ бюджета")</f>
         <v>ПРЕВЫШЕНИЕ бюджета</v>
       </c>
-      <c r="F64" s="48"/>
+      <c r="F64" s="46"/>
       <c r="L64" s="12" t="s">
         <v>174</v>
       </c>
@@ -11218,11 +11218,11 @@
       <c r="B65" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E65" s="50">
+      <c r="E65" s="48">
         <f>IFERROR(J51/SUM(Допущения!$C$8:$G$8),0)</f>
-        <v>1.3089023861526934</v>
-      </c>
-      <c r="F65" s="48"/>
+        <v>1.3097324386461318</v>
+      </c>
+      <c r="F65" s="46"/>
       <c r="L65" s="12" t="s">
         <v>176</v>
       </c>
@@ -11231,11 +11231,11 @@
       <c r="B66" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E66" s="50">
+      <c r="E66" s="48">
         <f>IFERROR(I51/Допущения!$G$7,0)</f>
-        <v>6.0826691080903208</v>
-      </c>
-      <c r="F66" s="48"/>
+        <v>6.0865024414236535</v>
+      </c>
+      <c r="F66" s="46"/>
       <c r="L66" s="12" t="s">
         <v>178</v>
       </c>
@@ -11244,11 +11244,11 @@
       <c r="B67" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="51">
+      <c r="E67" s="49">
         <f>IFERROR(J51/SUM(Допущения!$C$10:$G$10),0)</f>
-        <v>4.6420162815244921E-2</v>
-      </c>
-      <c r="F67" s="48"/>
+        <v>4.6449600588678787E-2</v>
+      </c>
+      <c r="F67" s="46"/>
       <c r="L67" s="12" t="s">
         <v>180</v>
       </c>
@@ -11257,11 +11257,11 @@
       <c r="B68" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E68" s="52">
+      <c r="E68" s="50">
         <f>IFERROR(J15/J51,0)</f>
-        <v>0.17997947908845238</v>
-      </c>
-      <c r="F68" s="48"/>
+        <v>0.17986541577981241</v>
+      </c>
+      <c r="F68" s="46"/>
       <c r="L68" s="12" t="s">
         <v>182</v>
       </c>
@@ -11270,11 +11270,11 @@
       <c r="B69" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="E69" s="52">
+      <c r="E69" s="50">
         <f>IFERROR(J32/J51,0)</f>
-        <v>0.53551912245966182</v>
-      </c>
-      <c r="F69" s="48"/>
+        <v>0.53517973330675894</v>
+      </c>
+      <c r="F69" s="46"/>
       <c r="L69" s="12" t="s">
         <v>184</v>
       </c>
@@ -11283,18 +11283,18 @@
       <c r="B70" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="52">
+      <c r="E70" s="50">
         <f>IFERROR(J40/J51,0)</f>
-        <v>0.11159385788055466</v>
-      </c>
-      <c r="F70" s="48"/>
+        <v>0.11152313445853887</v>
+      </c>
+      <c r="F70" s="46"/>
       <c r="L70" s="12" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="38" t="s">
+      <c r="B72" s="35" t="s">
         <v>187</v>
       </c>
       <c r="C72" s="36"/>
@@ -11309,22 +11309,22 @@
       <c r="L72" s="36"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="39" t="s">
+      <c r="B73" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40"/>
-      <c r="I73" s="40"/>
-      <c r="J73" s="40"/>
-      <c r="K73" s="40"/>
-      <c r="L73" s="41"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="39"/>
     </row>
     <row r="74" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="42"/>
+      <c r="B74" s="40"/>
       <c r="C74" s="36"/>
       <c r="D74" s="36"/>
       <c r="E74" s="36"/>
@@ -11334,20 +11334,20 @@
       <c r="I74" s="36"/>
       <c r="J74" s="36"/>
       <c r="K74" s="36"/>
-      <c r="L74" s="43"/>
+      <c r="L74" s="41"/>
     </row>
     <row r="75" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="44"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45"/>
-      <c r="I75" s="45"/>
-      <c r="J75" s="45"/>
-      <c r="K75" s="45"/>
-      <c r="L75" s="46"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="43"/>
+      <c r="D75" s="43"/>
+      <c r="E75" s="43"/>
+      <c r="F75" s="43"/>
+      <c r="G75" s="43"/>
+      <c r="H75" s="43"/>
+      <c r="I75" s="43"/>
+      <c r="J75" s="43"/>
+      <c r="K75" s="43"/>
+      <c r="L75" s="44"/>
     </row>
     <row r="76" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
